--- a/simple_transformer_emulator.xlsx
+++ b/simple_transformer_emulator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazek\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\simple-excel-transformer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{248D43D9-7BFF-4503-994F-F24B1DB6C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783DC78D-16E8-46D3-816B-117DE97313E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="1215" windowWidth="31305" windowHeight="19140" xr2:uid="{A717418E-B71A-4AAF-9520-624CD1656D70}"/>
+    <workbookView xWindow="1755" yWindow="780" windowWidth="31305" windowHeight="19140" xr2:uid="{29A3BCC4-0CC3-465F-85C9-DF7B56BC0285}"/>
   </bookViews>
   <sheets>
     <sheet name="base_model" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="85">
   <si>
     <t>vocab</t>
   </si>
@@ -202,9 +202,6 @@
     <t>softmax</t>
   </si>
   <si>
-    <t>value</t>
-  </si>
-  <si>
     <t>Output</t>
   </si>
   <si>
@@ -227,9 +224,6 @@
   </si>
   <si>
     <t>FNN(con)</t>
-  </si>
-  <si>
-    <t>Matricies</t>
   </si>
   <si>
     <t>FNN</t>
@@ -265,12 +259,6 @@
     <t>beta 1</t>
   </si>
   <si>
-    <t>ff1 bias</t>
-  </si>
-  <si>
-    <t>ff2 bias</t>
-  </si>
-  <si>
     <t>ReLU</t>
   </si>
   <si>
@@ -303,6 +291,33 @@
   <si>
     <t>B</t>
   </si>
+  <si>
+    <t>change</t>
+  </si>
+  <si>
+    <t>-&gt;</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>try to</t>
+  </si>
+  <si>
+    <t>&lt;-</t>
+  </si>
+  <si>
+    <t>Concant</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>FNN exp b</t>
+  </si>
+  <si>
+    <t>FNN con b</t>
+  </si>
 </sst>
 </file>
 
@@ -311,7 +326,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +346,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -403,7 +425,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -617,17 +639,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -677,16 +713,22 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,10 +755,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1059,28 +1097,28 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>1.8989480733899999</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>1.53782844543</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>1.01377952099</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>-2.23739480972</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>0.469589829445</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>-1.14724195004</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>-9.1805830597899998E-2</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="8">
         <v>-1.40178525448</v>
       </c>
     </row>
@@ -1404,173 +1442,203 @@
       </c>
     </row>
     <row r="17" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="C17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>15</v>
       </c>
-      <c r="K17" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="18" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="10">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),1)</f>
+      <c r="D18" s="9">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),1)</f>
         <v>1.8989480733899999</v>
       </c>
-      <c r="C18" s="11">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),2)</f>
+      <c r="E18" s="10">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),2)</f>
         <v>1.53782844543</v>
       </c>
-      <c r="D18" s="11">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),3)</f>
+      <c r="F18" s="10">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),3)</f>
         <v>1.01377952099</v>
       </c>
-      <c r="E18" s="11">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),4)</f>
+      <c r="G18" s="10">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),4)</f>
         <v>-2.23739480972</v>
       </c>
-      <c r="F18" s="11">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),5)</f>
+      <c r="H18" s="10">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),5)</f>
         <v>0.469589829445</v>
       </c>
-      <c r="G18" s="11">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),6)</f>
+      <c r="I18" s="10">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),6)</f>
         <v>-1.14724195004</v>
       </c>
-      <c r="H18" s="11">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),7)</f>
+      <c r="J18" s="10">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),7)</f>
         <v>-9.1805830597899998E-2</v>
       </c>
-      <c r="I18" s="12">
-        <f>INDEX($B$2:$I$13,MATCH($A18,$A$2:$A$13,0),8)</f>
+      <c r="K18" s="11">
+        <f>INDEX($B$2:$I$13,MATCH($C18,$A$2:$A$13,0),8)</f>
         <v>-1.40178525448</v>
       </c>
-      <c r="L18" s="63" t="str">
+      <c r="N18" s="57" t="str">
         <f>INDEX($B$158:$M$158,1,MATCH(MAX($B$162:$M$162),$B$162:$M$162,0))</f>
         <v>three</v>
       </c>
+      <c r="O18" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="P18" s="58" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="21">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),1)</f>
+      <c r="D19" s="20">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),1)</f>
         <v>-1.62172985077</v>
       </c>
-      <c r="C19" s="22">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),2)</f>
+      <c r="E19" s="21">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),2)</f>
         <v>0.90439116954800003</v>
       </c>
-      <c r="D19" s="22">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),3)</f>
+      <c r="F19" s="21">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),3)</f>
         <v>-0.75339096784600001</v>
       </c>
-      <c r="E19" s="22">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),4)</f>
+      <c r="G19" s="21">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),4)</f>
         <v>-0.50689250230799998</v>
       </c>
-      <c r="F19" s="22">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),5)</f>
+      <c r="H19" s="21">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),5)</f>
         <v>-1.2724831104300001</v>
       </c>
-      <c r="G19" s="22">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),6)</f>
+      <c r="I19" s="21">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),6)</f>
         <v>2.0163106918299998</v>
       </c>
-      <c r="H19" s="22">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),7)</f>
+      <c r="J19" s="21">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),7)</f>
         <v>-1.2519977092700001</v>
       </c>
-      <c r="I19" s="23">
-        <f>INDEX($B$2:$I$13,MATCH($A19,$A$2:$A$13,0),8)</f>
+      <c r="K19" s="22">
+        <f>INDEX($B$2:$I$13,MATCH($C19,$A$2:$A$13,0),8)</f>
         <v>-0.49855604767799999</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="24">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),1)</f>
+      <c r="D20" s="23">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),1)</f>
         <v>-0.40159517526600003</v>
       </c>
-      <c r="C20" s="25">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),2)</f>
+      <c r="E20" s="24">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),2)</f>
         <v>2.01237869263</v>
       </c>
-      <c r="D20" s="25">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),3)</f>
+      <c r="F20" s="24">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),3)</f>
         <v>0.113317415118</v>
       </c>
-      <c r="E20" s="25">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),4)</f>
+      <c r="G20" s="24">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),4)</f>
         <v>-1.6461256742499999</v>
       </c>
-      <c r="F20" s="25">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),5)</f>
+      <c r="H20" s="24">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),5)</f>
         <v>-1.0578277111100001</v>
       </c>
-      <c r="G20" s="25">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),6)</f>
+      <c r="I20" s="24">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),6)</f>
         <v>-0.73396754264800002</v>
       </c>
-      <c r="H20" s="25">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),7)</f>
+      <c r="J20" s="24">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),7)</f>
         <v>-0.42599785327900003</v>
       </c>
-      <c r="I20" s="26">
-        <f>INDEX($B$2:$I$13,MATCH($A20,$A$2:$A$13,0),8)</f>
+      <c r="K20" s="25">
+        <f>INDEX($B$2:$I$13,MATCH($C20,$A$2:$A$13,0),8)</f>
         <v>0.45491826534300001</v>
       </c>
-      <c r="K20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="27">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),1)</f>
-        <v>-0.884277224541</v>
-      </c>
-      <c r="C21" s="28">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),2)</f>
-        <v>-0.67542916536300002</v>
-      </c>
-      <c r="D21" s="28">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),3)</f>
-        <v>0.13021598756300001</v>
-      </c>
-      <c r="E21" s="28">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),4)</f>
-        <v>0.47523784637499999</v>
-      </c>
-      <c r="F21" s="28">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),5)</f>
-        <v>-0.38556727766999999</v>
-      </c>
-      <c r="G21" s="28">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),6)</f>
-        <v>1.06284892559</v>
-      </c>
-      <c r="H21" s="28">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),7)</f>
-        <v>-0.56175851821900002</v>
-      </c>
-      <c r="I21" s="29">
-        <f>INDEX($B$2:$I$13,MATCH($A21,$A$2:$A$13,0),8)</f>
-        <v>-0.71408510208099996</v>
-      </c>
-      <c r="L21" s="4">
+      <c r="N20" s="60">
         <f>MAX(B162:M162)</f>
         <v>0.99920655458234675</v>
+      </c>
+      <c r="O20" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="P20" s="58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="26">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),1)</f>
+        <v>-0.884277224541</v>
+      </c>
+      <c r="E21" s="27">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),2)</f>
+        <v>-0.67542916536300002</v>
+      </c>
+      <c r="F21" s="27">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),3)</f>
+        <v>0.13021598756300001</v>
+      </c>
+      <c r="G21" s="27">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),4)</f>
+        <v>0.47523784637499999</v>
+      </c>
+      <c r="H21" s="27">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),5)</f>
+        <v>-0.38556727766999999</v>
+      </c>
+      <c r="I21" s="27">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),6)</f>
+        <v>1.06284892559</v>
+      </c>
+      <c r="J21" s="27">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),7)</f>
+        <v>-0.56175851821900002</v>
+      </c>
+      <c r="K21" s="28">
+        <f>INDEX($B$2:$I$13,MATCH($C21,$A$2:$A$13,0),8)</f>
+        <v>-0.71408510208099996</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
@@ -1595,7 +1663,7 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" s="3">
         <v>0.309412002563</v>
@@ -1622,7 +1690,7 @@
         <v>0.71123671531699995</v>
       </c>
       <c r="K25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L25" s="3">
         <v>0.20037585496900001</v>
@@ -1649,7 +1717,7 @@
         <v>-0.50684213638300002</v>
       </c>
       <c r="U25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="V25" s="3">
         <v>-0.52028542756999996</v>
@@ -2342,301 +2410,301 @@
       </c>
     </row>
     <row r="37" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="10" cm="1">
-        <f t="array" ref="B37:I40">MMULT(B18:I21,B27:I34)+B25:I25</f>
+      <c r="B37" s="9" cm="1">
+        <f t="array" ref="B37:I40">MMULT(D18:K21,B27:I34)+B25:I25</f>
         <v>1.6651345569955176</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>-0.25132993599862519</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>-0.1103869035244659</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="10">
         <v>1.5308757410446381</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="10">
         <v>1.020494439791509</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="10">
         <v>-0.56291114657670938</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="10">
         <v>0.37850431485057373</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="11">
         <v>-0.61273221373829367</v>
       </c>
-      <c r="L37" s="10" cm="1">
-        <f t="array" ref="L37:S40">MMULT(B18:I21,L27:S34)+L25:S25</f>
+      <c r="L37" s="9" cm="1">
+        <f t="array" ref="L37:S40">MMULT(D18:K21,L27:S34)+L25:S25</f>
         <v>-6.9072969696620523E-3</v>
       </c>
-      <c r="M37" s="11">
+      <c r="M37" s="10">
         <v>0.60124970030043778</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="10">
         <v>1.3033874249846236</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37" s="10">
         <v>1.5287171085515812</v>
       </c>
-      <c r="P37" s="11">
+      <c r="P37" s="10">
         <v>-0.47726116072397562</v>
       </c>
-      <c r="Q37" s="11">
+      <c r="Q37" s="10">
         <v>-0.53711982421036497</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="10">
         <v>0.62321342311321104</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="11">
         <v>0.40495596027010472</v>
       </c>
-      <c r="V37" s="10" cm="1">
-        <f t="array" ref="V37:AC40">MMULT(B18:I21,V27:AC34)+V25:AC25</f>
+      <c r="V37" s="9" cm="1">
+        <f t="array" ref="V37:AC40">MMULT(D18:K21,V27:AC34)+V25:AC25</f>
         <v>1.6825300558680152</v>
       </c>
-      <c r="W37" s="11">
+      <c r="W37" s="10">
         <v>2.3953592121636507</v>
       </c>
-      <c r="X37" s="11">
+      <c r="X37" s="10">
         <v>-0.93785966644232499</v>
       </c>
-      <c r="Y37" s="11">
+      <c r="Y37" s="10">
         <v>1.0200758194347377</v>
       </c>
-      <c r="Z37" s="11">
+      <c r="Z37" s="10">
         <v>2.6636156843470107</v>
       </c>
-      <c r="AA37" s="11">
+      <c r="AA37" s="10">
         <v>0.91804438443679559</v>
       </c>
-      <c r="AB37" s="11">
+      <c r="AB37" s="10">
         <v>-0.36691057660090798</v>
       </c>
-      <c r="AC37" s="12">
+      <c r="AC37" s="11">
         <v>1.3890250945122895</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="21">
+      <c r="B38" s="20">
         <v>0.51019099700740422</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="21">
         <v>-0.1998963736519897</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>0.24221660676767676</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="21">
         <v>-1.5529357344029029</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="21">
         <v>-0.42936641562908001</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="21">
         <v>-0.26915916145363505</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="21">
         <v>-1.7277720706059498</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="22">
         <v>2.2053959015235858</v>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="20">
         <v>3.165433112601157E-2</v>
       </c>
-      <c r="M38" s="22">
+      <c r="M38" s="21">
         <v>0.34866312998042476</v>
       </c>
-      <c r="N38" s="22">
+      <c r="N38" s="21">
         <v>-0.66306866266215381</v>
       </c>
-      <c r="O38" s="22">
+      <c r="O38" s="21">
         <v>-1.1756872371691813</v>
       </c>
-      <c r="P38" s="22">
+      <c r="P38" s="21">
         <v>0.98165544307843944</v>
       </c>
-      <c r="Q38" s="22">
+      <c r="Q38" s="21">
         <v>-0.66573886051367248</v>
       </c>
-      <c r="R38" s="22">
+      <c r="R38" s="21">
         <v>1.9980977519149299</v>
       </c>
-      <c r="S38" s="23">
+      <c r="S38" s="22">
         <v>-0.11477807383903188</v>
       </c>
-      <c r="V38" s="21">
+      <c r="V38" s="20">
         <v>-1.8533183010155421</v>
       </c>
-      <c r="W38" s="22">
+      <c r="W38" s="21">
         <v>0.2234242120640742</v>
       </c>
-      <c r="X38" s="22">
+      <c r="X38" s="21">
         <v>-1.1430936512622405</v>
       </c>
-      <c r="Y38" s="22">
+      <c r="Y38" s="21">
         <v>0.5887969035557733</v>
       </c>
-      <c r="Z38" s="22">
+      <c r="Z38" s="21">
         <v>-0.17421063899550701</v>
       </c>
-      <c r="AA38" s="22">
+      <c r="AA38" s="21">
         <v>-0.14390024178896166</v>
       </c>
-      <c r="AB38" s="22">
+      <c r="AB38" s="21">
         <v>0.36951574122270625</v>
       </c>
-      <c r="AC38" s="23">
+      <c r="AC38" s="22">
         <v>-0.20605486209219553</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="24">
+      <c r="B39" s="23">
         <v>0.59300629300458574</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <v>0.21610794561326219</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="24">
         <v>-0.63836035514752487</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="24">
         <v>0.62957460884743222</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="24">
         <v>0.13416804145046651</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="24">
         <v>-0.86998725690621281</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="24">
         <v>-0.52595342264994138</v>
       </c>
-      <c r="I39" s="26">
+      <c r="I39" s="25">
         <v>-0.93021655971885486</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="23">
         <v>-0.18252052563476617</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="24">
         <v>0.17071400135002784</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="24">
         <v>0.67746759414472824</v>
       </c>
-      <c r="O39" s="25">
+      <c r="O39" s="24">
         <v>0.68144897959326278</v>
       </c>
-      <c r="P39" s="25">
+      <c r="P39" s="24">
         <v>0.45194182675279204</v>
       </c>
-      <c r="Q39" s="25">
+      <c r="Q39" s="24">
         <v>0.4635369312575997</v>
       </c>
-      <c r="R39" s="25">
+      <c r="R39" s="24">
         <v>1.5321031240125764</v>
       </c>
-      <c r="S39" s="26">
+      <c r="S39" s="25">
         <v>1.7483425769457897</v>
       </c>
-      <c r="V39" s="24">
+      <c r="V39" s="23">
         <v>0.52730376957005687</v>
       </c>
-      <c r="W39" s="25">
+      <c r="W39" s="24">
         <v>1.8963695805601941</v>
       </c>
-      <c r="X39" s="25">
+      <c r="X39" s="24">
         <v>-1.8909569008727809</v>
       </c>
-      <c r="Y39" s="25">
+      <c r="Y39" s="24">
         <v>1.329809502864721</v>
       </c>
-      <c r="Z39" s="25">
+      <c r="Z39" s="24">
         <v>1.5232690975202958</v>
       </c>
-      <c r="AA39" s="25">
+      <c r="AA39" s="24">
         <v>0.42137481557874751</v>
       </c>
-      <c r="AB39" s="25">
+      <c r="AB39" s="24">
         <v>0.52826963129948401</v>
       </c>
-      <c r="AC39" s="26">
+      <c r="AC39" s="25">
         <v>0.22070939063421444</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>0.24189961454675415</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="27">
         <v>-0.12487797932440649</v>
       </c>
-      <c r="D40" s="28">
+      <c r="D40" s="27">
         <v>0.87635800131821573</v>
       </c>
-      <c r="E40" s="28">
+      <c r="E40" s="27">
         <v>-1.7316410275813112</v>
       </c>
-      <c r="F40" s="28">
+      <c r="F40" s="27">
         <v>-0.31515131628059795</v>
       </c>
-      <c r="G40" s="28">
+      <c r="G40" s="27">
         <v>0.76045428151263061</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="27">
         <v>-0.82897544523340483</v>
       </c>
-      <c r="I40" s="29">
+      <c r="I40" s="28">
         <v>2.9651069141198523</v>
       </c>
-      <c r="L40" s="27">
+      <c r="L40" s="26">
         <v>0.23414625568263125</v>
       </c>
-      <c r="M40" s="28">
+      <c r="M40" s="27">
         <v>0.41917778927543664</v>
       </c>
-      <c r="N40" s="28">
+      <c r="N40" s="27">
         <v>-0.46869417457228008</v>
       </c>
-      <c r="O40" s="28">
+      <c r="O40" s="27">
         <v>-0.87347785038883929</v>
       </c>
-      <c r="P40" s="28">
+      <c r="P40" s="27">
         <v>0.65291676199134008</v>
       </c>
-      <c r="Q40" s="28">
+      <c r="Q40" s="27">
         <v>-0.53020674620943375</v>
       </c>
-      <c r="R40" s="28">
+      <c r="R40" s="27">
         <v>0.13318499363782643</v>
       </c>
-      <c r="S40" s="29">
+      <c r="S40" s="28">
         <v>-1.1361658653459805</v>
       </c>
-      <c r="V40" s="27">
+      <c r="V40" s="26">
         <v>-1.6541939357236153</v>
       </c>
-      <c r="W40" s="28">
+      <c r="W40" s="27">
         <v>-0.74243499293082182</v>
       </c>
-      <c r="X40" s="28">
+      <c r="X40" s="27">
         <v>0.45844664903923948</v>
       </c>
-      <c r="Y40" s="28">
+      <c r="Y40" s="27">
         <v>-0.4205297364155749</v>
       </c>
-      <c r="Z40" s="28">
+      <c r="Z40" s="27">
         <v>-0.71723766009708678</v>
       </c>
-      <c r="AA40" s="28">
+      <c r="AA40" s="27">
         <v>8.9503258932204094E-3</v>
       </c>
-      <c r="AB40" s="28">
+      <c r="AB40" s="27">
         <v>0.51773023506801708</v>
       </c>
-      <c r="AC40" s="29">
+      <c r="AC40" s="28">
         <v>-0.46972752722259548</v>
       </c>
     </row>
@@ -2666,422 +2734,422 @@
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AE41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <f>B37*COS($AE42)-C37*SIN($AE42)</f>
         <v>1.6651345569955176</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <f>B37*SIN($AE42)+C37*COS($AE42)</f>
         <v>-0.25132993599862519</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <f>D37*COS($AE42)-E37*SIN($AE42)</f>
         <v>-0.1103869035244659</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="10">
         <f>D37*SIN($AE42)+E37*COS($AE42)</f>
         <v>1.5308757410446381</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="10">
         <f>F37*COS($AE42)-G37*SIN($AE42)</f>
         <v>1.020494439791509</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="10">
         <f>F37*SIN($AE42)+G37*COS($AE42)</f>
         <v>-0.56291114657670938</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="10">
         <f>H37*COS($AE42)-I37*SIN($AE42)</f>
         <v>0.37850431485057373</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="11">
         <f>H37*SIN($AE42)+I37*COS($AE42)</f>
         <v>-0.61273221373829367</v>
       </c>
       <c r="K42" t="s">
-        <v>63</v>
-      </c>
-      <c r="L42" s="10">
+        <v>61</v>
+      </c>
+      <c r="L42" s="9">
         <f>L37*COS($AE42)-M37*SIN($AE42)</f>
         <v>-6.9072969696620523E-3</v>
       </c>
-      <c r="M42" s="11">
+      <c r="M42" s="10">
         <f>L37*SIN($AE42)+M37*COS($AE42)</f>
         <v>0.60124970030043778</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42" s="10">
         <f>N37*COS($AE42)-O37*SIN($AE42)</f>
         <v>1.3033874249846236</v>
       </c>
-      <c r="O42" s="11">
+      <c r="O42" s="10">
         <f>N37*SIN($AE42)+O37*COS($AE42)</f>
         <v>1.5287171085515812</v>
       </c>
-      <c r="P42" s="11">
+      <c r="P42" s="10">
         <f>P37*COS($AE42)-Q37*SIN($AE42)</f>
         <v>-0.47726116072397562</v>
       </c>
-      <c r="Q42" s="11">
+      <c r="Q42" s="10">
         <f>P37*SIN($AE42)+Q37*COS($AE42)</f>
         <v>-0.53711982421036497</v>
       </c>
-      <c r="R42" s="11">
+      <c r="R42" s="10">
         <f>R37*COS($AE42)-S37*SIN($AE42)</f>
         <v>0.62321342311321104</v>
       </c>
-      <c r="S42" s="12">
+      <c r="S42" s="11">
         <f>R37*SIN($AE42)+S37*COS($AE42)</f>
         <v>0.40495596027010472</v>
       </c>
       <c r="U42" t="s">
         <v>30</v>
       </c>
-      <c r="V42" s="10">
+      <c r="V42" s="9">
         <f>V37</f>
         <v>1.6825300558680152</v>
       </c>
-      <c r="W42" s="11">
+      <c r="W42" s="10">
         <f t="shared" ref="V42:AC45" si="0">W37</f>
         <v>2.3953592121636507</v>
       </c>
-      <c r="X42" s="11">
+      <c r="X42" s="10">
         <f t="shared" si="0"/>
         <v>-0.93785966644232499</v>
       </c>
-      <c r="Y42" s="11">
+      <c r="Y42" s="10">
         <f t="shared" si="0"/>
         <v>1.0200758194347377</v>
       </c>
-      <c r="Z42" s="11">
+      <c r="Z42" s="10">
         <f t="shared" si="0"/>
         <v>2.6636156843470107</v>
       </c>
-      <c r="AA42" s="11">
+      <c r="AA42" s="10">
         <f t="shared" si="0"/>
         <v>0.91804438443679559</v>
       </c>
-      <c r="AB42" s="11">
+      <c r="AB42" s="10">
         <f t="shared" si="0"/>
         <v>-0.36691057660090798</v>
       </c>
-      <c r="AC42" s="12">
+      <c r="AC42" s="11">
         <f t="shared" si="0"/>
         <v>1.3890250945122895</v>
       </c>
-      <c r="AE42" s="56">
+      <c r="AE42" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="21">
+      <c r="B43" s="20">
         <f>B38*COS($AE43)-C38*SIN($AE43)</f>
         <v>0.4438643705127327</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="21">
         <f>B38*SIN($AE43)+C38*COS($AE43)</f>
         <v>0.32130644907309369</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <f>D38*COS($AE43)-E38*SIN($AE43)</f>
         <v>1.437620552927517</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="21">
         <f>D38*SIN($AE43)+E38*COS($AE43)</f>
         <v>-0.6352365115292975</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="21">
         <f>F38*COS($AE43)-G38*SIN($AE43)</f>
         <v>-5.4980397682721227E-3</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="21">
         <f>F38*SIN($AE43)+G38*COS($AE43)</f>
         <v>-0.50672669618177246</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43" s="21">
         <f>H38*COS($AE43)-I38*SIN($AE43)</f>
         <v>-2.7892958949093156</v>
       </c>
-      <c r="I43" s="23">
+      <c r="I43" s="22">
         <f>H38*SIN($AE43)+I38*COS($AE43)</f>
         <v>-0.26228957483102877</v>
       </c>
-      <c r="L43" s="21">
+      <c r="L43" s="20">
         <f>L38*COS($AE43)-M38*SIN($AE43)</f>
         <v>-0.27628699925273398</v>
       </c>
-      <c r="M43" s="22">
+      <c r="M43" s="21">
         <f>L38*SIN($AE43)+M38*COS($AE43)</f>
         <v>0.21501969428566664</v>
       </c>
-      <c r="N43" s="22">
+      <c r="N43" s="21">
         <f>N38*COS($AE43)-O38*SIN($AE43)</f>
         <v>0.63104916990156057</v>
       </c>
-      <c r="O43" s="22">
+      <c r="O43" s="21">
         <f>N38*SIN($AE43)+O38*COS($AE43)</f>
         <v>-1.1931795657878288</v>
       </c>
-      <c r="P43" s="22">
+      <c r="P43" s="21">
         <f>P38*COS($AE43)-Q38*SIN($AE43)</f>
         <v>1.0905906340446179</v>
       </c>
-      <c r="Q43" s="22">
+      <c r="Q43" s="21">
         <f>P38*SIN($AE43)+Q38*COS($AE43)</f>
         <v>0.46633433098768129</v>
       </c>
-      <c r="R43" s="22">
+      <c r="R43" s="21">
         <f>R38*COS($AE43)-S38*SIN($AE43)</f>
         <v>1.1761592415372666</v>
       </c>
-      <c r="S43" s="23">
+      <c r="S43" s="22">
         <f>R38*SIN($AE43)+S38*COS($AE43)</f>
         <v>1.6193264250879675</v>
       </c>
       <c r="U43" t="s">
-        <v>74</v>
-      </c>
-      <c r="V43" s="21">
+        <v>70</v>
+      </c>
+      <c r="V43" s="20">
         <f>V38</f>
         <v>-1.8533183010155421</v>
       </c>
-      <c r="W43" s="22">
+      <c r="W43" s="21">
         <f t="shared" si="0"/>
         <v>0.2234242120640742</v>
       </c>
-      <c r="X43" s="22">
+      <c r="X43" s="21">
         <f t="shared" si="0"/>
         <v>-1.1430936512622405</v>
       </c>
-      <c r="Y43" s="22">
+      <c r="Y43" s="21">
         <f t="shared" si="0"/>
         <v>0.5887969035557733</v>
       </c>
-      <c r="Z43" s="22">
+      <c r="Z43" s="21">
         <f t="shared" si="0"/>
         <v>-0.17421063899550701</v>
       </c>
-      <c r="AA43" s="22">
+      <c r="AA43" s="21">
         <f t="shared" si="0"/>
         <v>-0.14390024178896166</v>
       </c>
-      <c r="AB43" s="22">
+      <c r="AB43" s="21">
         <f t="shared" si="0"/>
         <v>0.36951574122270625</v>
       </c>
-      <c r="AC43" s="23">
+      <c r="AC43" s="22">
         <f t="shared" si="0"/>
         <v>-0.20605486209219553</v>
       </c>
-      <c r="AE43" s="57">
+      <c r="AE43" s="65">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="24">
+      <c r="B44" s="23">
         <f>B39*COS($AE44)-C39*SIN($AE44)</f>
         <v>-0.44328409174912986</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="24">
         <f>B39*SIN($AE44)+C39*COS($AE44)</f>
         <v>0.44928645840084508</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="24">
         <f>D39*COS($AE44)-E39*SIN($AE44)</f>
         <v>-0.30681892944800232</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="24">
         <f>D39*SIN($AE44)+E39*COS($AE44)</f>
         <v>-0.84245491016543617</v>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="24">
         <f>F39*COS($AE44)-G39*SIN($AE44)</f>
         <v>0.73524356806061508</v>
       </c>
-      <c r="G44" s="25">
+      <c r="G44" s="24">
         <f>F39*SIN($AE44)+G39*COS($AE44)</f>
         <v>0.48404109965099712</v>
       </c>
-      <c r="H44" s="25">
+      <c r="H44" s="24">
         <f>H39*COS($AE44)-I39*SIN($AE44)</f>
         <v>1.0647173771499081</v>
       </c>
-      <c r="I44" s="26">
+      <c r="I44" s="25">
         <f>H39*SIN($AE44)+I39*COS($AE44)</f>
         <v>-9.1141415214984478E-2</v>
       </c>
-      <c r="L44" s="24">
+      <c r="L44" s="23">
         <f>L39*COS($AE44)-M39*SIN($AE44)</f>
         <v>-7.9274462802866708E-2</v>
       </c>
-      <c r="M44" s="25">
+      <c r="M44" s="24">
         <f>L39*SIN($AE44)+M39*COS($AE44)</f>
         <v>-0.23700753591868245</v>
       </c>
-      <c r="N44" s="25">
+      <c r="N44" s="24">
         <f>N39*COS($AE44)-O39*SIN($AE44)</f>
         <v>-0.90156579982367235</v>
       </c>
-      <c r="O44" s="25">
+      <c r="O44" s="24">
         <f>N39*SIN($AE44)+O39*COS($AE44)</f>
         <v>0.33243670298757211</v>
       </c>
-      <c r="P44" s="25">
+      <c r="P44" s="24">
         <f>P39*COS($AE44)-Q39*SIN($AE44)</f>
         <v>-0.60956710033771944</v>
       </c>
-      <c r="Q44" s="25">
+      <c r="Q44" s="24">
         <f>P39*SIN($AE44)+Q39*COS($AE44)</f>
         <v>0.21805011257559148</v>
       </c>
-      <c r="R44" s="25">
+      <c r="R44" s="24">
         <f>R39*COS($AE44)-S39*SIN($AE44)</f>
         <v>-2.2273432747484159</v>
       </c>
-      <c r="S44" s="26">
+      <c r="S44" s="25">
         <f>R39*SIN($AE44)+S39*COS($AE44)</f>
         <v>0.66557019569955489</v>
       </c>
-      <c r="V44" s="24">
+      <c r="V44" s="23">
         <f t="shared" si="0"/>
         <v>0.52730376957005687</v>
       </c>
-      <c r="W44" s="25">
+      <c r="W44" s="24">
         <f t="shared" si="0"/>
         <v>1.8963695805601941</v>
       </c>
-      <c r="X44" s="25">
+      <c r="X44" s="24">
         <f t="shared" si="0"/>
         <v>-1.8909569008727809</v>
       </c>
-      <c r="Y44" s="25">
+      <c r="Y44" s="24">
         <f t="shared" si="0"/>
         <v>1.329809502864721</v>
       </c>
-      <c r="Z44" s="25">
+      <c r="Z44" s="24">
         <f t="shared" si="0"/>
         <v>1.5232690975202958</v>
       </c>
-      <c r="AA44" s="25">
+      <c r="AA44" s="24">
         <f t="shared" si="0"/>
         <v>0.42137481557874751</v>
       </c>
-      <c r="AB44" s="25">
+      <c r="AB44" s="24">
         <f t="shared" si="0"/>
         <v>0.52826963129948401</v>
       </c>
-      <c r="AC44" s="26">
+      <c r="AC44" s="25">
         <f t="shared" si="0"/>
         <v>0.22070939063421444</v>
       </c>
-      <c r="AE44" s="57">
+      <c r="AE44" s="66">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="27">
+      <c r="B45" s="26">
         <f>B40*COS($AE45)-C40*SIN($AE45)</f>
         <v>-0.22185602188306638</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="27">
         <f>B40*SIN($AE45)+C40*COS($AE45)</f>
         <v>0.15776513807630471</v>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="27">
         <f>D40*COS($AE45)-E40*SIN($AE45)</f>
         <v>-0.62321864987172548</v>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="27">
         <f>D40*SIN($AE45)+E40*COS($AE45)</f>
         <v>1.8379832723203386</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="27">
         <f>F40*COS($AE45)-G40*SIN($AE45)</f>
         <v>0.2046821240753228</v>
       </c>
-      <c r="G45" s="28">
+      <c r="G45" s="27">
         <f>F40*SIN($AE45)+G40*COS($AE45)</f>
         <v>-0.79731818899878282</v>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="27">
         <f>H40*COS($AE45)-I40*SIN($AE45)</f>
         <v>0.4022435590281227</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="28">
         <f>H40*SIN($AE45)+I40*COS($AE45)</f>
         <v>-3.0524186181095248</v>
       </c>
-      <c r="L45" s="27">
+      <c r="L45" s="26">
         <f>L40*COS($AE45)-M40*SIN($AE45)</f>
         <v>-0.29095740923396129</v>
       </c>
-      <c r="M45" s="28">
+      <c r="M45" s="27">
         <f>L40*SIN($AE45)+M40*COS($AE45)</f>
         <v>-0.38194014463512432</v>
       </c>
-      <c r="N45" s="28">
+      <c r="N45" s="27">
         <f>N40*COS($AE45)-O40*SIN($AE45)</f>
         <v>0.58726891731388509</v>
       </c>
-      <c r="O45" s="28">
+      <c r="O45" s="27">
         <f>N40*SIN($AE45)+O40*COS($AE45)</f>
         <v>0.79859439213838446</v>
       </c>
-      <c r="P45" s="28">
+      <c r="P45" s="27">
         <f>P40*COS($AE45)-Q40*SIN($AE45)</f>
         <v>-0.57155991497761438</v>
       </c>
-      <c r="Q45" s="28">
+      <c r="Q45" s="27">
         <f>P40*SIN($AE45)+Q40*COS($AE45)</f>
         <v>0.61704031910891632</v>
       </c>
-      <c r="R45" s="28">
+      <c r="R45" s="27">
         <f>R40*COS($AE45)-S40*SIN($AE45)</f>
         <v>2.8483591713744566E-2</v>
       </c>
-      <c r="S45" s="29">
+      <c r="S45" s="28">
         <f>R40*SIN($AE45)+S40*COS($AE45)</f>
         <v>1.1435907489616961</v>
       </c>
-      <c r="V45" s="27">
+      <c r="V45" s="26">
         <f t="shared" si="0"/>
         <v>-1.6541939357236153</v>
       </c>
-      <c r="W45" s="28">
+      <c r="W45" s="27">
         <f t="shared" si="0"/>
         <v>-0.74243499293082182</v>
       </c>
-      <c r="X45" s="28">
+      <c r="X45" s="27">
         <f t="shared" si="0"/>
         <v>0.45844664903923948</v>
       </c>
-      <c r="Y45" s="28">
+      <c r="Y45" s="27">
         <f t="shared" si="0"/>
         <v>-0.4205297364155749</v>
       </c>
-      <c r="Z45" s="28">
+      <c r="Z45" s="27">
         <f t="shared" si="0"/>
         <v>-0.71723766009708678</v>
       </c>
-      <c r="AA45" s="28">
+      <c r="AA45" s="27">
         <f t="shared" si="0"/>
         <v>8.9503258932204094E-3</v>
       </c>
-      <c r="AB45" s="28">
+      <c r="AB45" s="27">
         <f t="shared" si="0"/>
         <v>0.51773023506801708</v>
       </c>
-      <c r="AC45" s="29">
+      <c r="AC45" s="28">
         <f t="shared" si="0"/>
         <v>-0.46972752722259548</v>
       </c>
-      <c r="AE45" s="58">
+      <c r="AE45" s="67">
         <v>3</v>
       </c>
     </row>
@@ -3121,19 +3189,19 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="K47" t="s">
-        <v>63</v>
-      </c>
-      <c r="L47" s="13" cm="1">
+        <v>61</v>
+      </c>
+      <c r="L47" s="12" cm="1">
         <f t="array" ref="L47:O54">TRANSPOSE(L42:S45)</f>
         <v>-6.9072969696620523E-3</v>
       </c>
-      <c r="M47" s="30">
+      <c r="M47" s="29">
         <v>-0.27628699925273398</v>
       </c>
-      <c r="N47" s="33">
+      <c r="N47" s="32">
         <v>-7.9274462802866708E-2</v>
       </c>
-      <c r="O47" s="36">
+      <c r="O47" s="35">
         <v>-0.29095740923396129</v>
       </c>
       <c r="P47" s="3"/>
@@ -3159,18 +3227,18 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="K48" t="s">
-        <v>73</v>
-      </c>
-      <c r="L48" s="14">
+        <v>69</v>
+      </c>
+      <c r="L48" s="13">
         <v>0.60124970030043778</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="30">
         <v>0.21501969428566664</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="33">
         <v>-0.23700753591868245</v>
       </c>
-      <c r="O48" s="37">
+      <c r="O48" s="36">
         <v>-0.38194014463512432</v>
       </c>
       <c r="P48" s="3"/>
@@ -3195,16 +3263,16 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="L49" s="14">
+      <c r="L49" s="13">
         <v>1.3033874249846236</v>
       </c>
-      <c r="M49" s="31">
+      <c r="M49" s="30">
         <v>0.63104916990156057</v>
       </c>
-      <c r="N49" s="34">
+      <c r="N49" s="33">
         <v>-0.90156579982367235</v>
       </c>
-      <c r="O49" s="37">
+      <c r="O49" s="36">
         <v>0.58726891731388509</v>
       </c>
       <c r="P49" s="3"/>
@@ -3229,16 +3297,16 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="L50" s="14">
+      <c r="L50" s="13">
         <v>1.5287171085515812</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="30">
         <v>-1.1931795657878288</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="33">
         <v>0.33243670298757211</v>
       </c>
-      <c r="O50" s="37">
+      <c r="O50" s="36">
         <v>0.79859439213838446</v>
       </c>
       <c r="P50" s="3"/>
@@ -3255,455 +3323,455 @@
       <c r="AC50" s="3"/>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="L51" s="15">
+      <c r="L51" s="14">
         <v>-0.47726116072397562</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="30">
         <v>1.0905906340446179</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="33">
         <v>-0.60956710033771944</v>
       </c>
-      <c r="O51" s="37">
+      <c r="O51" s="36">
         <v>-0.57155991497761438</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="L52" s="15">
+      <c r="L52" s="14">
         <v>-0.53711982421036497</v>
       </c>
-      <c r="M52" s="31">
+      <c r="M52" s="30">
         <v>0.46633433098768129</v>
       </c>
-      <c r="N52" s="34">
+      <c r="N52" s="33">
         <v>0.21805011257559148</v>
       </c>
-      <c r="O52" s="37">
+      <c r="O52" s="36">
         <v>0.61704031910891632</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="L53" s="15">
+      <c r="L53" s="14">
         <v>0.62321342311321104</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="30">
         <v>1.1761592415372666</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="33">
         <v>-2.2273432747484159</v>
       </c>
-      <c r="O53" s="37">
+      <c r="O53" s="36">
         <v>2.8483591713744566E-2</v>
       </c>
     </row>
     <row r="54" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L54" s="16">
+      <c r="L54" s="15">
         <v>0.40495596027010472</v>
       </c>
-      <c r="M54" s="32">
+      <c r="M54" s="31">
         <v>1.6193264250879675</v>
       </c>
-      <c r="N54" s="35">
+      <c r="N54" s="34">
         <v>0.66557019569955489</v>
       </c>
-      <c r="O54" s="38">
+      <c r="O54" s="37">
         <v>1.1435907489616961</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="3">
+        <v>71</v>
+      </c>
+      <c r="B56" s="45">
         <f t="shared" ref="B56:I56" si="1">B42-B37</f>
         <v>0</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L56" s="3">
+      <c r="L56" s="45">
         <f t="shared" ref="L56:S56" si="2">L42-L37</f>
         <v>0</v>
       </c>
-      <c r="M56" s="3">
+      <c r="M56" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O56" s="3">
+      <c r="O56" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P56" s="3">
+      <c r="P56" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R56" s="3">
+      <c r="R56" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S56" s="3">
+      <c r="S56" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V56" s="3">
+      <c r="V56" s="45">
         <f>V42-V37</f>
         <v>0</v>
       </c>
-      <c r="W56" s="3">
+      <c r="W56" s="46">
         <f t="shared" ref="W56:AC56" si="3">W42-W37</f>
         <v>0</v>
       </c>
-      <c r="X56" s="3">
+      <c r="X56" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y56" s="3">
+      <c r="Y56" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z56" s="3">
+      <c r="Z56" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA56" s="3">
+      <c r="AA56" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB56" s="3">
+      <c r="AB56" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC56" s="3">
+      <c r="AC56" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="3">
+        <v>72</v>
+      </c>
+      <c r="B57" s="48">
         <f t="shared" ref="B57:C57" si="4">B43-B38</f>
         <v>-6.6326626494671526E-2</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="68">
         <f t="shared" si="4"/>
         <v>0.52120282272508334</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="68">
         <f t="shared" ref="D57:I57" si="5">D43-D38</f>
         <v>1.1954039461598402</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="68">
         <f t="shared" si="5"/>
         <v>0.91769922287360539</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="68">
         <f t="shared" si="5"/>
         <v>0.42386837586080789</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="68">
         <f t="shared" si="5"/>
         <v>-0.23756753472813741</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="68">
         <f t="shared" si="5"/>
         <v>-1.0615238243033658</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="49">
         <f t="shared" si="5"/>
         <v>-2.4676854763546148</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="48">
         <f t="shared" ref="L57:S57" si="6">L43-L38</f>
         <v>-0.30794133037874555</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="68">
         <f t="shared" si="6"/>
         <v>-0.13364343569475812</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="68">
         <f t="shared" si="6"/>
         <v>1.2941178325637144</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="68">
         <f t="shared" si="6"/>
         <v>-1.7492328618647468E-2</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="68">
         <f t="shared" si="6"/>
         <v>0.10893519096617843</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="68">
         <f t="shared" si="6"/>
         <v>1.1320731915013538</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="68">
         <f t="shared" si="6"/>
         <v>-0.8219385103776633</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="49">
         <f t="shared" si="6"/>
         <v>1.7341044989269994</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="48">
         <f>V43-V38</f>
         <v>0</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="68">
         <f t="shared" ref="W57:AC57" si="7">W43-W38</f>
         <v>0</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="49">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B58" s="3">
+      <c r="B58" s="48">
         <f t="shared" ref="B58:I59" si="8">B44-B39</f>
         <v>-1.0362903847537157</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="68">
         <f t="shared" si="8"/>
         <v>0.23317851278758289</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="68">
         <f t="shared" si="8"/>
         <v>0.33154142569952255</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="68">
         <f t="shared" si="8"/>
         <v>-1.4720295190128683</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="68">
         <f t="shared" si="8"/>
         <v>0.60107552661014862</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="68">
         <f t="shared" si="8"/>
         <v>1.35402835655721</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="68">
         <f t="shared" si="8"/>
         <v>1.5906707997998495</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="49">
         <f t="shared" si="8"/>
         <v>0.83907514450387044</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="48">
         <f t="shared" ref="L58:S58" si="9">L44-L39</f>
         <v>0.10324606283189947</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="68">
         <f t="shared" si="9"/>
         <v>-0.4077215372687103</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="68">
         <f t="shared" si="9"/>
         <v>-1.5790333939684005</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="68">
         <f t="shared" si="9"/>
         <v>-0.34901227660569067</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="68">
         <f t="shared" si="9"/>
         <v>-1.0615089270905114</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="68">
         <f t="shared" si="9"/>
         <v>-0.24548681868200822</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="68">
         <f t="shared" si="9"/>
         <v>-3.7594463987609923</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="49">
         <f t="shared" si="9"/>
         <v>-1.0827723812462349</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="48">
         <f t="shared" ref="V58:AC58" si="10">V44-V39</f>
         <v>0</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="68">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="68">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="68">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="68">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="68">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="68">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="49">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B59" s="3">
+      <c r="B59" s="50">
         <f t="shared" si="8"/>
         <v>-0.46375563642982054</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="51">
         <f t="shared" si="8"/>
         <v>0.28264311740071119</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="51">
         <f t="shared" si="8"/>
         <v>-1.4995766511899413</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="51">
         <f t="shared" si="8"/>
         <v>3.5696242999016499</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="51">
         <f t="shared" si="8"/>
         <v>0.51983344035592072</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="51">
         <f t="shared" si="8"/>
         <v>-1.5577724705114133</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="51">
         <f t="shared" si="8"/>
         <v>1.2312190042615274</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="52">
         <f t="shared" si="8"/>
         <v>-6.017525532229377</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="50">
         <f t="shared" ref="L59:S59" si="11">L45-L40</f>
         <v>-0.52510366491659255</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="51">
         <f t="shared" si="11"/>
         <v>-0.80111793391056096</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="51">
         <f t="shared" si="11"/>
         <v>1.0559630918861651</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="51">
         <f t="shared" si="11"/>
         <v>1.6720722425272236</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="51">
         <f t="shared" si="11"/>
         <v>-1.2244766769689543</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="51">
         <f t="shared" si="11"/>
         <v>1.14724706531835</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="51">
         <f t="shared" si="11"/>
         <v>-0.10470140192408187</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="52">
         <f t="shared" si="11"/>
         <v>2.2797566143076766</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="50">
         <f t="shared" ref="V59:AC59" si="12">V45-V40</f>
         <v>0</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="51">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X59" s="3">
+      <c r="X59" s="51">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="51">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="51">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="51">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="51">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="52">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -3729,336 +3797,336 @@
       <c r="A62" t="s">
         <v>41</v>
       </c>
-      <c r="B62" s="17" t="str">
+      <c r="B62" s="16" t="str">
         <f>A63</f>
         <v>one</v>
       </c>
-      <c r="C62" s="18" t="str">
+      <c r="C62" s="17" t="str">
         <f>A64</f>
         <v>plus</v>
       </c>
-      <c r="D62" s="19" t="str">
+      <c r="D62" s="18" t="str">
         <f>A65</f>
         <v>two</v>
       </c>
-      <c r="E62" s="20" t="str">
+      <c r="E62" s="19" t="str">
         <f>A66</f>
         <v>equals</v>
       </c>
-      <c r="H62" s="17" t="str">
+      <c r="H62" s="16" t="str">
         <f>G63</f>
         <v>one</v>
       </c>
-      <c r="I62" s="18" t="str">
+      <c r="I62" s="17" t="str">
         <f>G64</f>
         <v>plus</v>
       </c>
-      <c r="J62" s="19" t="str">
+      <c r="J62" s="18" t="str">
         <f>G65</f>
         <v>two</v>
       </c>
-      <c r="K62" s="20" t="str">
+      <c r="K62" s="19" t="str">
         <f>G66</f>
         <v>equals</v>
       </c>
-      <c r="N62" s="17" t="str">
+      <c r="N62" s="16" t="str">
         <f>M63</f>
         <v>one</v>
       </c>
-      <c r="O62" s="18" t="str">
+      <c r="O62" s="17" t="str">
         <f>M64</f>
         <v>plus</v>
       </c>
-      <c r="P62" s="19" t="str">
+      <c r="P62" s="18" t="str">
         <f>M65</f>
         <v>two</v>
       </c>
-      <c r="Q62" s="20" t="str">
+      <c r="Q62" s="19" t="str">
         <f>M66</f>
         <v>equals</v>
       </c>
-      <c r="T62" s="17" t="str">
+      <c r="T62" s="16" t="str">
         <f>S63</f>
         <v>one</v>
       </c>
-      <c r="U62" s="18" t="str">
+      <c r="U62" s="17" t="str">
         <f>S64</f>
         <v>plus</v>
       </c>
-      <c r="V62" s="19" t="str">
+      <c r="V62" s="18" t="str">
         <f>S65</f>
         <v>two</v>
       </c>
-      <c r="W62" s="20" t="str">
+      <c r="W62" s="19" t="str">
         <f>S66</f>
         <v>equals</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="str">
-        <f>$A$18</f>
+      <c r="A63" s="16" t="str">
+        <f>$C$18</f>
         <v>one</v>
       </c>
-      <c r="B63" s="17" cm="1">
+      <c r="B63" s="16" cm="1">
         <f t="array" ref="B63:E66">MMULT(B42:C45,L47:O48)</f>
         <v>-0.16261362757531631</v>
       </c>
-      <c r="C63" s="40">
+      <c r="C63" s="39">
         <v>-0.51409591610758265</v>
       </c>
-      <c r="D63" s="41">
+      <c r="D63" s="40">
         <v>-7.2435558666674782E-2</v>
       </c>
-      <c r="E63" s="42">
+      <c r="E63" s="41">
         <v>-0.38849024462290421</v>
       </c>
-      <c r="G63" s="17" t="str">
-        <f>$A$18</f>
+      <c r="G63" s="16" t="str">
+        <f>$C$18</f>
         <v>one</v>
       </c>
-      <c r="H63" s="17" cm="1">
+      <c r="H63" s="16" cm="1">
         <f t="array" ref="H63:K66">MMULT(D42:E45,L49:O50)</f>
         <v>2.1963990344647386</v>
       </c>
-      <c r="I63" s="40">
+      <c r="I63" s="39">
         <v>-1.8962692158118797</v>
       </c>
-      <c r="J63" s="41">
+      <c r="J63" s="40">
         <v>0.60844034100262934</v>
       </c>
-      <c r="K63" s="42">
+      <c r="K63" s="41">
         <v>1.1577219845404962</v>
       </c>
-      <c r="M63" s="17" t="str">
-        <f>$A$18</f>
+      <c r="M63" s="16" t="str">
+        <f>$C$18</f>
         <v>one</v>
       </c>
-      <c r="N63" s="17" cm="1">
+      <c r="N63" s="16" cm="1">
         <f t="array" ref="N63:Q66">MMULT(F42:G45,L51:O52)</f>
         <v>-0.18469162475192169</v>
       </c>
-      <c r="O63" s="40">
+      <c r="O63" s="39">
         <v>0.85043688518687055</v>
       </c>
-      <c r="P63" s="41">
+      <c r="P63" s="40">
         <v>-0.74480267545558221</v>
       </c>
-      <c r="Q63" s="42">
+      <c r="Q63" s="41">
         <v>-0.93061258875602193</v>
       </c>
-      <c r="S63" s="17" t="str">
-        <f>$A$18</f>
+      <c r="S63" s="16" t="str">
+        <f>$C$18</f>
         <v>one</v>
       </c>
-      <c r="T63" s="17" cm="1">
+      <c r="T63" s="16" cm="1">
         <f t="array" ref="T63:W66">MMULT(H42:I45,L53:O54)</f>
         <v>-1.2240592281671125E-2</v>
       </c>
-      <c r="U63" s="40">
+      <c r="U63" s="39">
         <v>-0.5470321173358339</v>
       </c>
-      <c r="V63" s="41">
+      <c r="V63" s="40">
         <v>-1.2508753395548999</v>
       </c>
-      <c r="W63" s="42">
+      <c r="W63" s="41">
         <v>-0.68993372885583892</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="str">
-        <f>$A$19</f>
+      <c r="A64" s="17" t="str">
+        <f>$C$19</f>
         <v>plus</v>
       </c>
-      <c r="B64" s="40">
+      <c r="B64" s="39">
         <v>0.19011950318841192</v>
       </c>
-      <c r="C64" s="18">
+      <c r="C64" s="17">
         <v>-5.3546740552456895E-2</v>
       </c>
-      <c r="D64" s="43">
+      <c r="D64" s="42">
         <v>-0.11133915929932504</v>
       </c>
-      <c r="E64" s="44">
+      <c r="E64" s="43">
         <v>-0.25186545892682344</v>
       </c>
-      <c r="G64" s="18" t="str">
-        <f>$A$19</f>
+      <c r="G64" s="17" t="str">
+        <f>$C$19</f>
         <v>plus</v>
       </c>
-      <c r="H64" s="40">
+      <c r="H64" s="39">
         <v>0.90267962743370633</v>
       </c>
-      <c r="I64" s="18">
+      <c r="I64" s="17">
         <v>1.6651604815574346</v>
       </c>
-      <c r="J64" s="43">
+      <c r="J64" s="42">
         <v>-1.5072854551531734</v>
       </c>
-      <c r="K64" s="44">
+      <c r="K64" s="43">
         <v>0.33697354983708461</v>
       </c>
-      <c r="M64" s="18" t="str">
-        <f>$A$19</f>
+      <c r="M64" s="17" t="str">
+        <f>$C$19</f>
         <v>plus</v>
       </c>
-      <c r="N64" s="40">
+      <c r="N64" s="39">
         <v>0.27479695481736477</v>
       </c>
-      <c r="O64" s="18">
+      <c r="O64" s="17">
         <v>-0.24230016553440731</v>
       </c>
-      <c r="P64" s="43">
+      <c r="P64" s="42">
         <v>-0.10714038898840592</v>
       </c>
-      <c r="Q64" s="44">
+      <c r="Q64" s="43">
         <v>-0.30952834317051059</v>
       </c>
-      <c r="S64" s="18" t="str">
-        <f>$A$19</f>
+      <c r="S64" s="17" t="str">
+        <f>$C$19</f>
         <v>plus</v>
       </c>
-      <c r="T64" s="40">
+      <c r="T64" s="39">
         <v>-1.8445423693865988</v>
       </c>
-      <c r="U64" s="18">
+      <c r="U64" s="17">
         <v>-3.7053885837285248</v>
       </c>
-      <c r="V64" s="43">
+      <c r="V64" s="42">
         <v>6.0381473291593872</v>
       </c>
-      <c r="W64" s="44">
+      <c r="W64" s="43">
         <v>-0.37940109676528172</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A65" s="19" t="str">
-        <f>$A$20</f>
+      <c r="A65" s="18" t="str">
+        <f>$C$20</f>
         <v>two</v>
       </c>
-      <c r="B65" s="41">
+      <c r="B65" s="40">
         <v>0.27319524332619138</v>
       </c>
-      <c r="C65" s="43">
+      <c r="C65" s="42">
         <v>0.21907906845788028</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="18">
         <v>-7.134316818474698E-2</v>
       </c>
-      <c r="E65" s="45">
+      <c r="E65" s="44">
         <v>-4.2623744014265108E-2</v>
       </c>
-      <c r="G65" s="19" t="str">
-        <f>$A$20</f>
+      <c r="G65" s="18" t="str">
+        <f>$C$20</f>
         <v>two</v>
       </c>
-      <c r="H65" s="41">
+      <c r="H65" s="40">
         <v>-1.6877791687429582</v>
       </c>
-      <c r="I65" s="43">
+      <c r="I65" s="42">
         <v>0.81158215316877202</v>
       </c>
-      <c r="J65" s="19">
+      <c r="J65" s="18">
         <v>-3.4454792222577413E-3</v>
       </c>
-      <c r="K65" s="45">
+      <c r="K65" s="44">
         <v>-0.85296498739589743</v>
       </c>
-      <c r="M65" s="19" t="str">
-        <f>$A$20</f>
+      <c r="M65" s="18" t="str">
+        <f>$C$20</f>
         <v>two</v>
       </c>
-      <c r="N65" s="41">
+      <c r="N65" s="40">
         <v>-0.61089126906258184</v>
       </c>
-      <c r="O65" s="43">
+      <c r="O65" s="42">
         <v>1.0275747314447425</v>
       </c>
-      <c r="P65" s="19">
+      <c r="P65" s="18">
         <v>-0.3426350735545548</v>
       </c>
-      <c r="Q65" s="45">
+      <c r="Q65" s="44">
         <v>-0.12156287665808096</v>
       </c>
-      <c r="S65" s="19" t="str">
-        <f>$A$20</f>
+      <c r="S65" s="18" t="str">
+        <f>$C$20</f>
         <v>two</v>
       </c>
-      <c r="T65" s="41">
+      <c r="T65" s="40">
         <v>0.62663790194295355</v>
       </c>
-      <c r="U65" s="43">
+      <c r="U65" s="42">
         <v>1.1046894806826448</v>
       </c>
-      <c r="V65" s="19">
+      <c r="V65" s="18">
         <v>-2.4321520990635923</v>
       </c>
-      <c r="W65" s="45">
+      <c r="W65" s="44">
         <v>-7.3901504225866055E-2</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="str">
-        <f>$A$21</f>
+      <c r="A66" s="19" t="str">
+        <f>$C$21</f>
         <v>equals</v>
       </c>
-      <c r="B66" s="42">
+      <c r="B66" s="41">
         <v>9.6388667413889573E-2</v>
       </c>
-      <c r="C66" s="44">
+      <c r="C66" s="43">
         <v>9.5218546310324309E-2</v>
       </c>
-      <c r="D66" s="45">
+      <c r="D66" s="44">
         <v>-1.980400967497456E-2</v>
       </c>
-      <c r="E66" s="20">
+      <c r="E66" s="19">
         <v>4.2938136948058384E-3</v>
       </c>
-      <c r="G66" s="20" t="str">
-        <f>$A$21</f>
+      <c r="G66" s="19" t="str">
+        <f>$C$21</f>
         <v>equals</v>
       </c>
-      <c r="H66" s="42">
+      <c r="H66" s="41">
         <v>1.9974611223690197</v>
       </c>
-      <c r="I66" s="44">
+      <c r="I66" s="43">
         <v>-2.5863256944611979</v>
       </c>
-      <c r="J66" s="45">
+      <c r="J66" s="44">
         <v>1.1728857197331137</v>
       </c>
-      <c r="K66" s="20">
+      <c r="K66" s="19">
         <v>1.10180619235919</v>
       </c>
-      <c r="M66" s="20" t="str">
-        <f>$A$21</f>
+      <c r="M66" s="19" t="str">
+        <f>$C$21</f>
         <v>equals</v>
       </c>
-      <c r="N66" s="42">
+      <c r="N66" s="41">
         <v>0.33056857739911544</v>
       </c>
-      <c r="O66" s="44">
+      <c r="O66" s="43">
         <v>-0.14859243677815157</v>
       </c>
-      <c r="P66" s="45">
+      <c r="P66" s="44">
         <v>-0.29862280973331112</v>
       </c>
-      <c r="Q66" s="20">
+      <c r="Q66" s="19">
         <v>-0.60896556720508122</v>
       </c>
-      <c r="S66" s="20" t="str">
-        <f>$A$21</f>
+      <c r="S66" s="19" t="str">
+        <f>$C$21</f>
         <v>equals</v>
       </c>
-      <c r="T66" s="42">
+      <c r="T66" s="41">
         <v>-0.98541152729573145</v>
       </c>
-      <c r="U66" s="44">
+      <c r="U66" s="43">
         <v>-4.469759649435483</v>
       </c>
-      <c r="V66" s="45">
+      <c r="V66" s="44">
         <v>-2.9275333430242778</v>
       </c>
-      <c r="W66" s="20">
+      <c r="W66" s="19">
         <v>-3.4792603523236565</v>
       </c>
     </row>
@@ -4387,6 +4455,9 @@
       <c r="A74" t="s">
         <v>43</v>
       </c>
+      <c r="V74" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B75" s="2">
@@ -4453,9 +4524,6 @@
         <f>T69+$Z$75</f>
         <v>-1000000000.4878569</v>
       </c>
-      <c r="V75" t="s">
-        <v>44</v>
-      </c>
       <c r="W75">
         <v>0</v>
       </c>
@@ -4703,24 +4771,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>45</v>
-      </c>
       <c r="B80" t="str">
-        <f>A18</f>
+        <f>C18</f>
         <v>one</v>
       </c>
       <c r="C80" t="str">
-        <f>A19</f>
+        <f>C19</f>
         <v>plus</v>
       </c>
       <c r="D80" t="str">
-        <f>A20</f>
+        <f>C20</f>
         <v>two</v>
       </c>
       <c r="E80" t="str">
-        <f>A21</f>
+        <f>C21</f>
         <v>equals</v>
       </c>
       <c r="H80" t="str" cm="1">
@@ -4765,22 +4835,22 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="str" cm="1">
-        <f t="array" ref="A81:A84">A18:A21</f>
+        <f t="array" ref="A81:A84">C18:C21</f>
         <v>one</v>
       </c>
       <c r="B81" s="1">
         <f>EXP(B75-MAX($B75:$E75))/(EXP(B75-MAX($B75:$E75))+EXP(C75-MAX($B75:$E75))+EXP(D75-MAX($B75:$E75))+EXP(E75-MAX($B75:$E75)))</f>
         <v>1</v>
       </c>
-      <c r="C81" s="5">
+      <c r="C81" s="4">
         <f>EXP(C75-MAX($B75:$E75))/(EXP(B75-MAX($B75:$E75))+EXP(C75-MAX($B75:$E75))+EXP(D75-MAX($B75:$E75))+EXP(E75-MAX($B75:$E75)))</f>
         <v>0</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="4">
         <f>EXP(D75-MAX($B75:$E75))/(EXP(B75-MAX($B75:$E75))+EXP(C75-MAX($B75:$E75))+EXP(D75-MAX($B75:$E75))+EXP(E75-MAX($B75:$E75)))</f>
         <v>0</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="4">
         <f>EXP(E75-MAX($B75:$E75))/(EXP(B75-MAX($B75:$E75))+EXP(C75-MAX($B75:$E75))+EXP(D75-MAX($B75:$E75))+EXP(E75-MAX($B75:$E75)))</f>
         <v>0</v>
       </c>
@@ -4792,15 +4862,15 @@
         <f>EXP(G75-MAX($G75:$J75))/(EXP(G75-MAX($G75:$J75))+EXP(H75-MAX($G75:$J75))+EXP(I75-MAX($G75:$J75))+EXP(J75-MAX($G75:$J75)))</f>
         <v>1</v>
       </c>
-      <c r="I81" s="5">
+      <c r="I81" s="4">
         <f>EXP(H75-MAX($G75:$J75))/(EXP(G75-MAX($G75:$J75))+EXP(H75-MAX($G75:$J75))+EXP(I75-MAX($G75:$J75))+EXP(J75-MAX($G75:$J75)))</f>
         <v>0</v>
       </c>
-      <c r="J81" s="5">
+      <c r="J81" s="4">
         <f>EXP(I75-MAX($G75:$J75))/(EXP(G75-MAX($G75:$J75))+EXP(H75-MAX($G75:$J75))+EXP(I75-MAX($G75:$J75))+EXP(J75-MAX($G75:$J75)))</f>
         <v>0</v>
       </c>
-      <c r="K81" s="5">
+      <c r="K81" s="4">
         <f>EXP(J75-MAX($G75:$J75))/(EXP(G75-MAX($G75:$J75))+EXP(H75-MAX($G75:$J75))+EXP(I75-MAX($G75:$J75))+EXP(J75-MAX($G75:$J75)))</f>
         <v>0</v>
       </c>
@@ -4812,15 +4882,15 @@
         <f>EXP(L75-MAX($L75:$O75))/(EXP(L75-MAX($L75:$O75))+EXP(M75-MAX($L75:$O75))+EXP(N75-MAX($L75:$O75))+EXP(O75-MAX($L75:$O75)))</f>
         <v>1</v>
       </c>
-      <c r="O81" s="5">
+      <c r="O81" s="4">
         <f>EXP(M75-MAX($L75:$O75))/(EXP(L75-MAX($L75:$O75))+EXP(M75-MAX($L75:$O75))+EXP(N75-MAX($L75:$O75))+EXP(O75-MAX($L75:$O75)))</f>
         <v>0</v>
       </c>
-      <c r="P81" s="5">
+      <c r="P81" s="4">
         <f>EXP(N75-MAX($L75:$O75))/(EXP(L75-MAX($L75:$O75))+EXP(M75-MAX($L75:$O75))+EXP(N75-MAX($L75:$O75))+EXP(O75-MAX($L75:$O75)))</f>
         <v>0</v>
       </c>
-      <c r="Q81" s="5">
+      <c r="Q81" s="4">
         <f>EXP(O75-MAX($L75:$O75))/(EXP(L75-MAX($L75:$O75))+EXP(M75-MAX($L75:$O75))+EXP(N75-MAX($L75:$O75))+EXP(O75-MAX($L75:$O75)))</f>
         <v>0</v>
       </c>
@@ -4832,15 +4902,15 @@
         <f>EXP(Q75-MAX($Q75:$T75))/(EXP(Q75-MAX($Q75:$T75))+EXP(R75-MAX($Q75:$T75))+EXP(S75-MAX($Q75:$T75))+EXP(T75-MAX($Q75:$T75)))</f>
         <v>1</v>
       </c>
-      <c r="U81" s="5">
+      <c r="U81" s="4">
         <f>EXP(R75-MAX($Q75:$T75))/(EXP(Q75-MAX($Q75:$T75))+EXP(R75-MAX($Q75:$T75))+EXP(S75-MAX($Q75:$T75))+EXP(T75-MAX($Q75:$T75)))</f>
         <v>0</v>
       </c>
-      <c r="V81" s="5">
+      <c r="V81" s="4">
         <f>EXP(S75-MAX($Q75:$T75))/(EXP(Q75-MAX($Q75:$T75))+EXP(R75-MAX($Q75:$T75))+EXP(S75-MAX($Q75:$T75))+EXP(T75-MAX($Q75:$T75)))</f>
         <v>0</v>
       </c>
-      <c r="W81" s="5">
+      <c r="W81" s="4">
         <f>EXP(T75-MAX($Q75:$T75))/(EXP(Q75-MAX($Q75:$T75))+EXP(R75-MAX($Q75:$T75))+EXP(S75-MAX($Q75:$T75))+EXP(T75-MAX($Q75:$T75)))</f>
         <v>0</v>
       </c>
@@ -4857,11 +4927,11 @@
         <f>EXP(C76-MAX($B76:$E76))/(EXP(B76-MAX($B76:$E76))+EXP(C76-MAX($B76:$E76))+EXP(D76-MAX($B76:$E76))+EXP(E76-MAX($B76:$E76)))</f>
         <v>0.45703173266826963</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="4">
         <f>EXP(D76-MAX($B76:$E76))/(EXP(B76-MAX($B76:$E76))+EXP(C76-MAX($B76:$E76))+EXP(D76-MAX($B76:$E76))+EXP(E76-MAX($B76:$E76)))</f>
         <v>0</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="4">
         <f>EXP(E76-MAX($B76:$E76))/(EXP(B76-MAX($B76:$E76))+EXP(C76-MAX($B76:$E76))+EXP(D76-MAX($B76:$E76))+EXP(E76-MAX($B76:$E76)))</f>
         <v>0</v>
       </c>
@@ -4876,11 +4946,11 @@
         <f>EXP(H76-MAX($G76:$J76))/(EXP(G76-MAX($G76:$J76))+EXP(H76-MAX($G76:$J76))+EXP(I76-MAX($G76:$J76))+EXP(J76-MAX($G76:$J76)))</f>
         <v>0.63161591630856806</v>
       </c>
-      <c r="J82" s="5">
+      <c r="J82" s="4">
         <f>EXP(I76-MAX($G76:$J76))/(EXP(G76-MAX($G76:$J76))+EXP(H76-MAX($G76:$J76))+EXP(I76-MAX($G76:$J76))+EXP(J76-MAX($G76:$J76)))</f>
         <v>0</v>
       </c>
-      <c r="K82" s="5">
+      <c r="K82" s="4">
         <f>EXP(J76-MAX($G76:$J76))/(EXP(G76-MAX($G76:$J76))+EXP(H76-MAX($G76:$J76))+EXP(I76-MAX($G76:$J76))+EXP(J76-MAX($G76:$J76)))</f>
         <v>0</v>
       </c>
@@ -4895,11 +4965,11 @@
         <f>EXP(M76-MAX($L76:$O76))/(EXP(L76-MAX($L76:$O76))+EXP(M76-MAX($L76:$O76))+EXP(N76-MAX($L76:$O76))+EXP(O76-MAX($L76:$O76)))</f>
         <v>0.40959427334236331</v>
       </c>
-      <c r="P82" s="5">
+      <c r="P82" s="4">
         <f>EXP(N76-MAX($L76:$O76))/(EXP(L76-MAX($L76:$O76))+EXP(M76-MAX($L76:$O76))+EXP(N76-MAX($L76:$O76))+EXP(O76-MAX($L76:$O76)))</f>
         <v>0</v>
       </c>
-      <c r="Q82" s="5">
+      <c r="Q82" s="4">
         <f>EXP(O76-MAX($L76:$O76))/(EXP(L76-MAX($L76:$O76))+EXP(M76-MAX($L76:$O76))+EXP(N76-MAX($L76:$O76))+EXP(O76-MAX($L76:$O76)))</f>
         <v>0</v>
       </c>
@@ -4914,11 +4984,11 @@
         <f>EXP(R76-MAX($Q76:$T76))/(EXP(Q76-MAX($Q76:$T76))+EXP(R76-MAX($Q76:$T76))+EXP(S76-MAX($Q76:$T76))+EXP(T76-MAX($Q76:$T76)))</f>
         <v>0.21151508136956554</v>
       </c>
-      <c r="V82" s="5">
+      <c r="V82" s="4">
         <f>EXP(S76-MAX($Q76:$T76))/(EXP(Q76-MAX($Q76:$T76))+EXP(R76-MAX($Q76:$T76))+EXP(S76-MAX($Q76:$T76))+EXP(T76-MAX($Q76:$T76)))</f>
         <v>0</v>
       </c>
-      <c r="W82" s="5">
+      <c r="W82" s="4">
         <f>EXP(T76-MAX($Q76:$T76))/(EXP(Q76-MAX($Q76:$T76))+EXP(R76-MAX($Q76:$T76))+EXP(S76-MAX($Q76:$T76))+EXP(T76-MAX($Q76:$T76)))</f>
         <v>0</v>
       </c>
@@ -4939,7 +5009,7 @@
         <f>EXP(D77-MAX($B77:$E77))/(EXP(B77-MAX($B77:$E77))+EXP(C77-MAX($B77:$E77))+EXP(D77-MAX($B77:$E77))+EXP(E77-MAX($B77:$E77)))</f>
         <v>0.28540174294939391</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="4">
         <f>EXP(E77-MAX($B77:$E77))/(EXP(B77-MAX($B77:$E77))+EXP(C77-MAX($B77:$E77))+EXP(D77-MAX($B77:$E77))+EXP(E77-MAX($B77:$E77)))</f>
         <v>0</v>
       </c>
@@ -4958,7 +5028,7 @@
         <f>EXP(I77-MAX($G77:$J77))/(EXP(G77-MAX($G77:$J77))+EXP(H77-MAX($G77:$J77))+EXP(I77-MAX($G77:$J77))+EXP(J77-MAX($G77:$J77)))</f>
         <v>0.32431952850844764</v>
       </c>
-      <c r="K83" s="5">
+      <c r="K83" s="4">
         <f>EXP(J77-MAX($G77:$J77))/(EXP(G77-MAX($G77:$J77))+EXP(H77-MAX($G77:$J77))+EXP(I77-MAX($G77:$J77))+EXP(J77-MAX($G77:$J77)))</f>
         <v>0</v>
       </c>
@@ -4977,7 +5047,7 @@
         <f>EXP(N77-MAX($L77:$O77))/(EXP(L77-MAX($L77:$O77))+EXP(M77-MAX($L77:$O77))+EXP(N77-MAX($L77:$O77))+EXP(O77-MAX($L77:$O77)))</f>
         <v>0.2241035525991075</v>
       </c>
-      <c r="Q83" s="5">
+      <c r="Q83" s="4">
         <f>EXP(O77-MAX($L77:$O77))/(EXP(L77-MAX($L77:$O77))+EXP(M77-MAX($L77:$O77))+EXP(N77-MAX($L77:$O77))+EXP(O77-MAX($L77:$O77)))</f>
         <v>0</v>
       </c>
@@ -4996,7 +5066,7 @@
         <f>EXP(S77-MAX($Q77:$T77))/(EXP(Q77-MAX($Q77:$T77))+EXP(R77-MAX($Q77:$T77))+EXP(S77-MAX($Q77:$T77))+EXP(T77-MAX($Q77:$T77)))</f>
         <v>4.5682944799536239E-2</v>
       </c>
-      <c r="W83" s="5">
+      <c r="W83" s="4">
         <f>EXP(T77-MAX($Q77:$T77))/(EXP(Q77-MAX($Q77:$T77))+EXP(R77-MAX($Q77:$T77))+EXP(S77-MAX($Q77:$T77))+EXP(T77-MAX($Q77:$T77)))</f>
         <v>0</v>
       </c>
@@ -5080,8 +5150,8 @@
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>46</v>
+      <c r="A86" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="B86" t="s">
         <v>31</v>
@@ -5097,116 +5167,119 @@
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B87" s="46" cm="1">
+      <c r="A87" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B87" s="45" cm="1">
         <f t="array" ref="B87:C90">MMULT(B81:E84,V42:W45)</f>
         <v>1.6825300558680152</v>
       </c>
-      <c r="C87" s="48">
+      <c r="C87" s="47">
         <v>2.3953592121636507</v>
       </c>
-      <c r="D87" s="46" cm="1">
+      <c r="D87" s="45" cm="1">
         <f t="array" ref="D87:E90">MMULT(H81:K84,X42:Y45)</f>
         <v>-0.93785966644232499</v>
       </c>
-      <c r="E87" s="48">
+      <c r="E87" s="47">
         <v>1.0200758194347377</v>
       </c>
-      <c r="F87" s="46" cm="1">
+      <c r="F87" s="45" cm="1">
         <f t="array" ref="F87:G90">MMULT(N81:Q84,Z42:AA45)</f>
         <v>2.6636156843470107</v>
       </c>
-      <c r="G87" s="48">
+      <c r="G87" s="47">
         <v>0.91804438443679559</v>
       </c>
-      <c r="H87" s="46" cm="1">
+      <c r="H87" s="45" cm="1">
         <f t="array" ref="H87:I90">MMULT(T81:W84,AB42:AC45)</f>
         <v>-0.36691057660090798</v>
       </c>
-      <c r="I87" s="48">
+      <c r="I87" s="47">
         <v>1.3890250945122895</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B88" s="49">
+      <c r="B88" s="48">
         <v>6.6535154869268642E-2</v>
       </c>
-      <c r="C88" s="50">
+      <c r="C88" s="49">
         <v>1.4027159958252826</v>
       </c>
-      <c r="D88" s="49">
+      <c r="D88" s="48">
         <v>-1.0674887178220147</v>
       </c>
-      <c r="E88" s="50">
+      <c r="E88" s="49">
         <v>0.74767319179727965</v>
       </c>
-      <c r="F88" s="49">
+      <c r="F88" s="48">
         <v>1.5012582735657016</v>
       </c>
-      <c r="G88" s="50">
+      <c r="G88" s="49">
         <v>0.48307794692802891</v>
       </c>
-      <c r="H88" s="49">
+      <c r="H88" s="48">
         <v>-0.21114530406375662</v>
       </c>
-      <c r="I88" s="50">
+      <c r="I88" s="49">
         <v>1.0516416277001286</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B89" s="49">
+      <c r="B89" s="48">
         <v>0.11363970195777146</v>
       </c>
-      <c r="C89" s="50">
+      <c r="C89" s="49">
         <v>1.4917621652762487</v>
       </c>
-      <c r="D89" s="49">
+      <c r="D89" s="48">
         <v>-1.3654112334131403</v>
       </c>
-      <c r="E89" s="50">
+      <c r="E89" s="49">
         <v>0.87163115892697696</v>
       </c>
-      <c r="F89" s="49">
+      <c r="F89" s="48">
         <v>0.73228457027469429</v>
       </c>
-      <c r="G89" s="50">
+      <c r="G89" s="49">
         <v>0.17964609273497306</v>
       </c>
-      <c r="H89" s="49">
+      <c r="H89" s="48">
         <v>8.4207994136709985E-2</v>
       </c>
-      <c r="I89" s="50">
+      <c r="I89" s="49">
         <v>0.44711841956435822</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B90" s="51">
+      <c r="B90" s="50">
         <v>-0.31977363778289575</v>
       </c>
-      <c r="C90" s="53">
+      <c r="C90" s="52">
         <v>0.95139322530967163</v>
       </c>
-      <c r="D90" s="51">
+      <c r="D90" s="50">
         <v>-0.84333513141121552</v>
       </c>
-      <c r="E90" s="53">
+      <c r="E90" s="52">
         <v>0.73405445907345168</v>
       </c>
-      <c r="F90" s="51">
+      <c r="F90" s="50">
         <v>1.097106274589158</v>
       </c>
-      <c r="G90" s="53">
+      <c r="G90" s="52">
         <v>0.38009703067939848</v>
       </c>
-      <c r="H90" s="51">
+      <c r="H90" s="50">
         <v>-7.4773152371091334E-2</v>
       </c>
-      <c r="I90" s="53">
+      <c r="I90" s="52">
         <v>0.89204669161449246</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B92" s="3">
         <v>-0.227685257792</v>
@@ -5235,7 +5308,7 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B93" s="3">
         <v>0.304691195488</v>
@@ -5262,7 +5335,7 @@
         <v>-0.34127610921899998</v>
       </c>
       <c r="K93" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L93" s="3">
         <v>8.43232646585E-2</v>
@@ -5291,7 +5364,7 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B94" s="3">
         <v>0.236791700125</v>
@@ -5450,7 +5523,7 @@
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B101" s="3" cm="1">
         <f t="array" ref="B101:I104">MMULT(B87:I90,B92:I99)+L93:S93</f>
@@ -5480,7 +5553,7 @@
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B102" s="3">
         <v>1.1019005417539109</v>
@@ -5571,79 +5644,79 @@
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B106" s="3">
-        <f t="shared" ref="B106:I109" si="17">B18+B101</f>
+        <f>D18+B101</f>
         <v>3.5660798027907079</v>
       </c>
       <c r="C106" s="3">
-        <f t="shared" si="17"/>
+        <f>E18+C101</f>
         <v>2.1074833214469444</v>
       </c>
       <c r="D106" s="3">
-        <f t="shared" si="17"/>
+        <f>F18+D101</f>
         <v>-2.04200760287475</v>
       </c>
       <c r="E106" s="3">
-        <f t="shared" si="17"/>
+        <f>G18+E101</f>
         <v>-2.4119042521110439</v>
       </c>
       <c r="F106" s="3">
-        <f t="shared" si="17"/>
+        <f>H18+F101</f>
         <v>-0.73130233431594127</v>
       </c>
       <c r="G106" s="3">
-        <f t="shared" si="17"/>
+        <f>I18+G101</f>
         <v>1.8047475715584216</v>
       </c>
       <c r="H106" s="3">
-        <f t="shared" si="17"/>
+        <f>J18+H101</f>
         <v>0.47362152962710985</v>
       </c>
       <c r="I106" s="3">
-        <f t="shared" si="17"/>
+        <f>K18+I101</f>
         <v>-4.6008185757561293</v>
       </c>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B107" s="3">
-        <f t="shared" si="17"/>
+        <f>D19+B102</f>
         <v>-0.51982930901608904</v>
       </c>
       <c r="C107" s="3">
-        <f t="shared" si="17"/>
+        <f>E19+C102</f>
         <v>1.3479919237706699</v>
       </c>
       <c r="D107" s="3">
-        <f t="shared" si="17"/>
+        <f>F19+D102</f>
         <v>-2.0279601722335001</v>
       </c>
       <c r="E107" s="3">
-        <f t="shared" si="17"/>
+        <f>G19+E102</f>
         <v>-0.80741010637309385</v>
       </c>
       <c r="F107" s="3">
-        <f t="shared" si="17"/>
+        <f>H19+F102</f>
         <v>-1.8730214703620578</v>
       </c>
       <c r="G107" s="3">
-        <f t="shared" si="17"/>
+        <f>I19+G102</f>
         <v>3.1467997924642277</v>
       </c>
       <c r="H107" s="3">
-        <f t="shared" si="17"/>
+        <f>J19+H102</f>
         <v>-0.27452593154292637</v>
       </c>
       <c r="I107" s="3">
-        <f t="shared" si="17"/>
+        <f>K19+I102</f>
         <v>-2.0822868797507761</v>
       </c>
       <c r="K107" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L107" s="3">
         <v>0.94048166275</v>
@@ -5672,39 +5745,39 @@
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B108" s="3">
-        <f t="shared" si="17"/>
+        <f>D20+B103</f>
         <v>0.39839789538604214</v>
       </c>
       <c r="C108" s="3">
-        <f t="shared" si="17"/>
+        <f>E20+C103</f>
         <v>2.5737780024847732</v>
       </c>
       <c r="D108" s="3">
-        <f t="shared" si="17"/>
+        <f>F20+D103</f>
         <v>-0.91748026252853465</v>
       </c>
       <c r="E108" s="3">
-        <f t="shared" si="17"/>
+        <f>G20+E103</f>
         <v>-1.4397014306894098</v>
       </c>
       <c r="F108" s="3">
-        <f t="shared" si="17"/>
+        <f>H20+F103</f>
         <v>-1.9407974634243539</v>
       </c>
       <c r="G108" s="3">
-        <f t="shared" si="17"/>
+        <f>I20+G103</f>
         <v>9.5002889729421836E-2</v>
       </c>
       <c r="H108" s="3">
-        <f t="shared" si="17"/>
+        <f>J20+H103</f>
         <v>0.48791753626430362</v>
       </c>
       <c r="I108" s="3">
-        <f t="shared" si="17"/>
+        <f>K20+I103</f>
         <v>-1.1935093982048466</v>
       </c>
       <c r="K108" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L108" s="3">
         <v>7.3604807257699995E-2</v>
@@ -5730,65 +5803,65 @@
       <c r="S108" s="3">
         <v>0.133196815848</v>
       </c>
-      <c r="U108" s="46">
+      <c r="U108" s="45">
         <v>0.65380156040199999</v>
       </c>
-      <c r="V108" s="47">
+      <c r="V108" s="46">
         <v>0.63998925685899999</v>
       </c>
-      <c r="W108" s="47">
+      <c r="W108" s="46">
         <v>0.46523708105099998</v>
       </c>
-      <c r="X108" s="47">
+      <c r="X108" s="46">
         <v>0.27787324786200002</v>
       </c>
-      <c r="Y108" s="47">
+      <c r="Y108" s="46">
         <v>-0.76043921709100004</v>
       </c>
-      <c r="Z108" s="47">
+      <c r="Z108" s="46">
         <v>-0.54799133539199996</v>
       </c>
-      <c r="AA108" s="47">
+      <c r="AA108" s="46">
         <v>-0.79614955186799996</v>
       </c>
-      <c r="AB108" s="48">
+      <c r="AB108" s="47">
         <v>2.7787254657600001E-3</v>
       </c>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B109" s="3">
-        <f t="shared" si="17"/>
+        <f>D21+B104</f>
         <v>7.5422761880695632E-2</v>
       </c>
       <c r="C109" s="3">
-        <f t="shared" si="17"/>
+        <f>E21+C104</f>
         <v>-0.26274988097222152</v>
       </c>
       <c r="D109" s="3">
-        <f t="shared" si="17"/>
+        <f>F21+D104</f>
         <v>-0.5246154725651927</v>
       </c>
       <c r="E109" s="3">
-        <f t="shared" si="17"/>
+        <f>G21+E104</f>
         <v>7.4397644852005784E-2</v>
       </c>
       <c r="F109" s="3">
-        <f t="shared" si="17"/>
+        <f>H21+F104</f>
         <v>-0.73512712042314898</v>
       </c>
       <c r="G109" s="3">
-        <f t="shared" si="17"/>
+        <f>I21+G104</f>
         <v>1.5672121742346437</v>
       </c>
       <c r="H109" s="3">
-        <f t="shared" si="17"/>
+        <f>J21+H104</f>
         <v>0.43770069074734985</v>
       </c>
       <c r="I109" s="3">
-        <f t="shared" si="17"/>
+        <f>K21+I104</f>
         <v>-1.6739077387459003</v>
       </c>
-      <c r="U109" s="49">
+      <c r="U109" s="48">
         <v>0.20386174321200001</v>
       </c>
       <c r="V109" s="3">
@@ -5809,7 +5882,7 @@
       <c r="AA109" s="3">
         <v>-0.49994936585400002</v>
       </c>
-      <c r="AB109" s="50">
+      <c r="AB109" s="49">
         <v>3.1892407685500002E-2</v>
       </c>
     </row>
@@ -5822,7 +5895,7 @@
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
-      <c r="U110" s="49">
+      <c r="U110" s="48">
         <v>-0.16467547416700001</v>
       </c>
       <c r="V110" s="3">
@@ -5843,47 +5916,47 @@
       <c r="AA110" s="3">
         <v>0.58368521928799999</v>
       </c>
-      <c r="AB110" s="50">
+      <c r="AB110" s="49">
         <v>0.61310625076299996</v>
       </c>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B111" s="3">
-        <f t="shared" ref="B111:I114" si="18">(B106-AVERAGE($B106:$I106))/SQRT(VARP($B106:$I106)+0.00001)*L$107+L$108</f>
+        <f t="shared" ref="B111:I114" si="17">(B106-AVERAGE($B106:$I106))/SQRT(VARP($B106:$I106)+0.00001)*L$107+L$108</f>
         <v>1.474887015657476</v>
       </c>
       <c r="C111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.69808123856544246</v>
       </c>
       <c r="D111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.9797374071664432</v>
       </c>
       <c r="E111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-1.0820240106514849</v>
       </c>
       <c r="F111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.33922661677543314</v>
       </c>
       <c r="G111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.61976678130313978</v>
       </c>
       <c r="H111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.24342656168252047</v>
       </c>
       <c r="I111" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-1.9570546308860888</v>
       </c>
-      <c r="U111" s="49">
+      <c r="U111" s="48">
         <v>1.73986461014E-2</v>
       </c>
       <c r="V111" s="3">
@@ -5904,44 +5977,44 @@
       <c r="AA111" s="3">
         <v>9.9300898611500002E-2</v>
       </c>
-      <c r="AB111" s="50">
+      <c r="AB111" s="49">
         <v>0.285685300827</v>
       </c>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>2.9087856860061934E-4</v>
       </c>
       <c r="C112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.77650710447440718</v>
       </c>
       <c r="D112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-1.2478800561255443</v>
       </c>
       <c r="E112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.41754566288626571</v>
       </c>
       <c r="F112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.3382901089289998</v>
       </c>
       <c r="G112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1.7978652817957681</v>
       </c>
       <c r="H112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>5.583898239299432E-2</v>
       </c>
       <c r="I112" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-1.0725638158677704</v>
       </c>
-      <c r="U112" s="49">
+      <c r="U112" s="48">
         <v>0.56751167774199995</v>
       </c>
       <c r="V112" s="3">
@@ -5962,44 +6035,44 @@
       <c r="AA112" s="3">
         <v>-0.83745300769800002</v>
       </c>
-      <c r="AB112" s="50">
+      <c r="AB112" s="49">
         <v>-0.71408480405800001</v>
       </c>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.5184459993877184</v>
       </c>
       <c r="C113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1.6579899218771978</v>
       </c>
       <c r="D113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.74835426085489332</v>
       </c>
       <c r="E113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-1.1120979710721735</v>
       </c>
       <c r="F113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.72896590230312308</v>
       </c>
       <c r="G113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.10744786557565884</v>
       </c>
       <c r="H113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.47772469855986793</v>
       </c>
       <c r="I113" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.72265857759385443</v>
       </c>
-      <c r="U113" s="49">
+      <c r="U113" s="48">
         <v>5.4811954498300001E-2</v>
       </c>
       <c r="V113" s="3">
@@ -6020,44 +6093,44 @@
       <c r="AA113" s="3">
         <v>0.44285315275199999</v>
       </c>
-      <c r="AB113" s="50">
+      <c r="AB113" s="49">
         <v>-0.74208664894099996</v>
       </c>
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.29310598798936122</v>
       </c>
       <c r="C114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.18381936803451049</v>
       </c>
       <c r="D114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.69271190666892235</v>
       </c>
       <c r="E114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.10230960268904524</v>
       </c>
       <c r="F114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-0.15522057139048728</v>
       </c>
       <c r="G114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>1.6713603881500119</v>
       </c>
       <c r="H114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.57162629997073366</v>
       </c>
       <c r="I114" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>-2.000823568626902</v>
       </c>
-      <c r="U114" s="49">
+      <c r="U114" s="48">
         <v>-2.5637572631199999E-2</v>
       </c>
       <c r="V114" s="3">
@@ -6078,12 +6151,12 @@
       <c r="AA114" s="3">
         <v>-1.8807819113100002E-2</v>
       </c>
-      <c r="AB114" s="50">
+      <c r="AB114" s="49">
         <v>0.29220953583699999</v>
       </c>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="U115" s="49">
+      <c r="U115" s="48">
         <v>0.69779258966400004</v>
       </c>
       <c r="V115" s="3">
@@ -6104,65 +6177,67 @@
       <c r="AA115" s="3">
         <v>-0.57231515645999997</v>
       </c>
-      <c r="AB115" s="50">
+      <c r="AB115" s="49">
         <v>-0.45132011175199999</v>
       </c>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A116" s="59" t="s">
+      <c r="A116" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B116" s="46">
+        <v>0.65855908393899998</v>
+      </c>
+      <c r="C116" s="46">
+        <v>0.247375965118</v>
+      </c>
+      <c r="D116" s="46">
+        <v>-0.40510380268099999</v>
+      </c>
+      <c r="E116" s="46">
+        <v>-0.30686187744100002</v>
+      </c>
+      <c r="F116" s="46">
+        <v>-0.14562746882399999</v>
+      </c>
+      <c r="G116" s="46">
+        <v>0.90137368440599996</v>
+      </c>
+      <c r="H116" s="46">
+        <v>-6.2352117151000003E-2</v>
+      </c>
+      <c r="I116" s="46">
+        <v>-3.9771486073699999E-2</v>
+      </c>
+      <c r="J116" s="46">
+        <v>0.42983087897299999</v>
+      </c>
+      <c r="K116" s="46">
+        <v>-6.6882461309399996E-2</v>
+      </c>
+      <c r="L116" s="46">
+        <v>6.9349870085699997E-2</v>
+      </c>
+      <c r="M116" s="46">
+        <v>0.95749187469499997</v>
+      </c>
+      <c r="N116" s="46">
+        <v>0.61053276061999995</v>
+      </c>
+      <c r="O116" s="46">
+        <v>0.32307174801799998</v>
+      </c>
+      <c r="P116" s="46">
+        <v>0.105392359197</v>
+      </c>
+      <c r="Q116" s="46">
+        <v>0.32801157236099998</v>
+      </c>
+      <c r="R116" s="56"/>
+      <c r="S116" s="56"/>
+      <c r="T116" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="B116" s="47">
-        <v>0.65855908393899998</v>
-      </c>
-      <c r="C116" s="47">
-        <v>0.247375965118</v>
-      </c>
-      <c r="D116" s="47">
-        <v>-0.40510380268099999</v>
-      </c>
-      <c r="E116" s="47">
-        <v>-0.30686187744100002</v>
-      </c>
-      <c r="F116" s="47">
-        <v>-0.14562746882399999</v>
-      </c>
-      <c r="G116" s="47">
-        <v>0.90137368440599996</v>
-      </c>
-      <c r="H116" s="47">
-        <v>-6.2352117151000003E-2</v>
-      </c>
-      <c r="I116" s="47">
-        <v>-3.9771486073699999E-2</v>
-      </c>
-      <c r="J116" s="47">
-        <v>0.42983087897299999</v>
-      </c>
-      <c r="K116" s="47">
-        <v>-6.6882461309399996E-2</v>
-      </c>
-      <c r="L116" s="47">
-        <v>6.9349870085699997E-2</v>
-      </c>
-      <c r="M116" s="47">
-        <v>0.95749187469499997</v>
-      </c>
-      <c r="N116" s="47">
-        <v>0.61053276061999995</v>
-      </c>
-      <c r="O116" s="47">
-        <v>0.32307174801799998</v>
-      </c>
-      <c r="P116" s="47">
-        <v>0.105392359197</v>
-      </c>
-      <c r="Q116" s="47">
-        <v>0.32801157236099998</v>
-      </c>
-      <c r="R116" s="62"/>
-      <c r="S116" s="62"/>
-      <c r="T116" s="62"/>
       <c r="U116" s="3">
         <v>-0.14338347315800001</v>
       </c>
@@ -6184,60 +6259,58 @@
       <c r="AA116" s="3">
         <v>9.9942788481700004E-2</v>
       </c>
-      <c r="AB116" s="50">
+      <c r="AB116" s="49">
         <v>-0.16301779449000001</v>
       </c>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A117" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B117" s="61">
+      <c r="A117" s="55"/>
+      <c r="B117" s="3">
         <v>7.0561140775699999E-2</v>
       </c>
-      <c r="C117" s="61">
+      <c r="C117" s="3">
         <v>0.42614600062399999</v>
       </c>
-      <c r="D117" s="61">
+      <c r="D117" s="3">
         <v>0.41959446668599998</v>
       </c>
-      <c r="E117" s="61">
+      <c r="E117" s="3">
         <v>-0.17956934869300001</v>
       </c>
-      <c r="F117" s="61">
+      <c r="F117" s="3">
         <v>9.4637416303199995E-2</v>
       </c>
-      <c r="G117" s="61">
+      <c r="G117" s="3">
         <v>5.0651889294400003E-2</v>
       </c>
-      <c r="H117" s="61">
+      <c r="H117" s="3">
         <v>0.37737256288499998</v>
       </c>
-      <c r="I117" s="61">
+      <c r="I117" s="3">
         <v>0.35482695698700001</v>
       </c>
-      <c r="J117" s="61">
+      <c r="J117" s="3">
         <v>-8.2411095500000003E-2</v>
       </c>
-      <c r="K117" s="61">
+      <c r="K117" s="3">
         <v>0.14026488363699999</v>
       </c>
-      <c r="L117" s="61">
+      <c r="L117" s="3">
         <v>-0.559133410454</v>
       </c>
-      <c r="M117" s="61">
+      <c r="M117" s="3">
         <v>-0.39692488312700003</v>
       </c>
-      <c r="N117" s="61">
+      <c r="N117" s="3">
         <v>-0.43756300210999999</v>
       </c>
-      <c r="O117" s="61">
+      <c r="O117" s="3">
         <v>0.34393057227099999</v>
       </c>
-      <c r="P117" s="61">
+      <c r="P117" s="3">
         <v>0.240622773767</v>
       </c>
-      <c r="Q117" s="61">
+      <c r="Q117" s="3">
         <v>0.57430642843199997</v>
       </c>
       <c r="U117" s="3">
@@ -6261,60 +6334,58 @@
       <c r="AA117" s="3">
         <v>9.5666348934199993E-2</v>
       </c>
-      <c r="AB117" s="50">
+      <c r="AB117" s="49">
         <v>3.7558041512999997E-2</v>
       </c>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A118" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B118" s="61">
+      <c r="A118" s="55"/>
+      <c r="B118" s="3">
         <v>-0.96964406967200001</v>
       </c>
-      <c r="C118" s="61">
+      <c r="C118" s="3">
         <v>-1.1537457816300001E-2</v>
       </c>
-      <c r="D118" s="61">
+      <c r="D118" s="3">
         <v>0.43790012598</v>
       </c>
-      <c r="E118" s="61">
+      <c r="E118" s="3">
         <v>8.2289956510100001E-2</v>
       </c>
-      <c r="F118" s="61">
+      <c r="F118" s="3">
         <v>-0.131339415908</v>
       </c>
-      <c r="G118" s="61">
+      <c r="G118" s="3">
         <v>-0.54552716016799996</v>
       </c>
-      <c r="H118" s="61">
+      <c r="H118" s="3">
         <v>-0.66841453313800003</v>
       </c>
-      <c r="I118" s="61">
+      <c r="I118" s="3">
         <v>2.86512766033E-2</v>
       </c>
-      <c r="J118" s="61">
+      <c r="J118" s="3">
         <v>-0.25135299563399999</v>
       </c>
-      <c r="K118" s="61">
+      <c r="K118" s="3">
         <v>0.101983785629</v>
       </c>
-      <c r="L118" s="61">
+      <c r="L118" s="3">
         <v>-0.34035906195600002</v>
       </c>
-      <c r="M118" s="61">
+      <c r="M118" s="3">
         <v>-0.88881808519399996</v>
       </c>
-      <c r="N118" s="61">
+      <c r="N118" s="3">
         <v>-0.90412408113499998</v>
       </c>
-      <c r="O118" s="61">
+      <c r="O118" s="3">
         <v>0.105749756098</v>
       </c>
-      <c r="P118" s="61">
+      <c r="P118" s="3">
         <v>-0.11779485642900001</v>
       </c>
-      <c r="Q118" s="61">
+      <c r="Q118" s="3">
         <v>-0.65865451097500005</v>
       </c>
       <c r="U118" s="3">
@@ -6338,58 +6409,58 @@
       <c r="AA118" s="3">
         <v>8.6163461208299999E-2</v>
       </c>
-      <c r="AB118" s="50">
+      <c r="AB118" s="49">
         <v>0.59569793939600002</v>
       </c>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A119" s="60"/>
-      <c r="B119" s="61">
+      <c r="A119" s="55"/>
+      <c r="B119" s="3">
         <v>-0.49029433727299998</v>
       </c>
-      <c r="C119" s="61">
+      <c r="C119" s="3">
         <v>0.38741406798400002</v>
       </c>
-      <c r="D119" s="61">
+      <c r="D119" s="3">
         <v>0.21850000321900001</v>
       </c>
-      <c r="E119" s="61">
+      <c r="E119" s="3">
         <v>5.66964671016E-2</v>
       </c>
-      <c r="F119" s="61">
+      <c r="F119" s="3">
         <v>-0.85554009675999998</v>
       </c>
-      <c r="G119" s="61">
+      <c r="G119" s="3">
         <v>-0.35538703203200001</v>
       </c>
-      <c r="H119" s="61">
+      <c r="H119" s="3">
         <v>0.47944489121400002</v>
       </c>
-      <c r="I119" s="61">
+      <c r="I119" s="3">
         <v>-0.309967726469</v>
       </c>
-      <c r="J119" s="61">
+      <c r="J119" s="3">
         <v>-0.23641389608400001</v>
       </c>
-      <c r="K119" s="61">
+      <c r="K119" s="3">
         <v>-9.5074167475099995E-3</v>
       </c>
-      <c r="L119" s="61">
+      <c r="L119" s="3">
         <v>0.111535705626</v>
       </c>
-      <c r="M119" s="61">
+      <c r="M119" s="3">
         <v>-0.246281698346</v>
       </c>
-      <c r="N119" s="61">
+      <c r="N119" s="3">
         <v>2.12625041604E-2</v>
       </c>
-      <c r="O119" s="61">
+      <c r="O119" s="3">
         <v>0.121678113937</v>
       </c>
-      <c r="P119" s="61">
+      <c r="P119" s="3">
         <v>-0.55345153808600001</v>
       </c>
-      <c r="Q119" s="61">
+      <c r="Q119" s="3">
         <v>0.220316708088</v>
       </c>
       <c r="U119" s="3">
@@ -6413,58 +6484,58 @@
       <c r="AA119" s="3">
         <v>-0.97540676593800002</v>
       </c>
-      <c r="AB119" s="50">
+      <c r="AB119" s="49">
         <v>-0.22055871784700001</v>
       </c>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A120" s="60"/>
-      <c r="B120" s="61">
+      <c r="A120" s="55"/>
+      <c r="B120" s="3">
         <v>0.85011291503899999</v>
       </c>
-      <c r="C120" s="61">
+      <c r="C120" s="3">
         <v>-0.78871428966500001</v>
       </c>
-      <c r="D120" s="61">
+      <c r="D120" s="3">
         <v>-0.24905468523499999</v>
       </c>
-      <c r="E120" s="61">
+      <c r="E120" s="3">
         <v>0.76109379529999999</v>
       </c>
-      <c r="F120" s="61">
+      <c r="F120" s="3">
         <v>0.41902032494500002</v>
       </c>
-      <c r="G120" s="61">
+      <c r="G120" s="3">
         <v>6.2750196084400004E-3</v>
       </c>
-      <c r="H120" s="61">
+      <c r="H120" s="3">
         <v>-0.25957578420600003</v>
       </c>
-      <c r="I120" s="61">
+      <c r="I120" s="3">
         <v>0.76983606815299999</v>
       </c>
-      <c r="J120" s="61">
+      <c r="J120" s="3">
         <v>-0.35612946748699997</v>
       </c>
-      <c r="K120" s="61">
+      <c r="K120" s="3">
         <v>-0.36290910840000001</v>
       </c>
-      <c r="L120" s="61">
+      <c r="L120" s="3">
         <v>0.70325994491599997</v>
       </c>
-      <c r="M120" s="61">
+      <c r="M120" s="3">
         <v>0.54860377311700004</v>
       </c>
-      <c r="N120" s="61">
+      <c r="N120" s="3">
         <v>0.33109995722800001</v>
       </c>
-      <c r="O120" s="61">
+      <c r="O120" s="3">
         <v>8.1417590379700006E-2</v>
       </c>
-      <c r="P120" s="61">
+      <c r="P120" s="3">
         <v>0.30222597718200001</v>
       </c>
-      <c r="Q120" s="61">
+      <c r="Q120" s="3">
         <v>-0.29892024397900002</v>
       </c>
       <c r="U120" s="3">
@@ -6488,58 +6559,58 @@
       <c r="AA120" s="3">
         <v>0.39396139979400002</v>
       </c>
-      <c r="AB120" s="50">
+      <c r="AB120" s="49">
         <v>0.42450684308999997</v>
       </c>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A121" s="60"/>
-      <c r="B121" s="61">
+      <c r="A121" s="55"/>
+      <c r="B121" s="3">
         <v>3.8962129503499997E-2</v>
       </c>
-      <c r="C121" s="61">
+      <c r="C121" s="3">
         <v>0.155238643289</v>
       </c>
-      <c r="D121" s="61">
+      <c r="D121" s="3">
         <v>-0.57461971044500004</v>
       </c>
-      <c r="E121" s="61">
+      <c r="E121" s="3">
         <v>0.32973256707199999</v>
       </c>
-      <c r="F121" s="61">
+      <c r="F121" s="3">
         <v>-0.36737698316599998</v>
       </c>
-      <c r="G121" s="61">
+      <c r="G121" s="3">
         <v>0.34713563323000002</v>
       </c>
-      <c r="H121" s="61">
+      <c r="H121" s="3">
         <v>-5.74187301099E-2</v>
       </c>
-      <c r="I121" s="61">
+      <c r="I121" s="3">
         <v>-0.52558648586300005</v>
       </c>
-      <c r="J121" s="61">
+      <c r="J121" s="3">
         <v>-8.5049621760799998E-2</v>
       </c>
-      <c r="K121" s="61">
+      <c r="K121" s="3">
         <v>0.124303549528</v>
       </c>
-      <c r="L121" s="61">
+      <c r="L121" s="3">
         <v>0.53730392456099996</v>
       </c>
-      <c r="M121" s="61">
+      <c r="M121" s="3">
         <v>0.104916885495</v>
       </c>
-      <c r="N121" s="61">
+      <c r="N121" s="3">
         <v>3.0407175421699999E-2</v>
       </c>
-      <c r="O121" s="61">
+      <c r="O121" s="3">
         <v>5.5369436740899999E-3</v>
       </c>
-      <c r="P121" s="61">
+      <c r="P121" s="3">
         <v>-0.11621550470600001</v>
       </c>
-      <c r="Q121" s="61">
+      <c r="Q121" s="3">
         <v>8.5723702795800002E-4</v>
       </c>
       <c r="U121" s="3">
@@ -6563,58 +6634,58 @@
       <c r="AA121" s="3">
         <v>-0.128914415836</v>
       </c>
-      <c r="AB121" s="50">
+      <c r="AB121" s="49">
         <v>1.6130566597E-2</v>
       </c>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A122" s="60"/>
-      <c r="B122" s="61">
+      <c r="A122" s="55"/>
+      <c r="B122" s="3">
         <v>-0.33994796872100003</v>
       </c>
-      <c r="C122" s="61">
+      <c r="C122" s="3">
         <v>0.50937128067000004</v>
       </c>
-      <c r="D122" s="61">
+      <c r="D122" s="3">
         <v>-9.2155367136000005E-2</v>
       </c>
-      <c r="E122" s="61">
+      <c r="E122" s="3">
         <v>-6.2681235372999994E-2</v>
       </c>
-      <c r="F122" s="61">
+      <c r="F122" s="3">
         <v>-0.54875582456600003</v>
       </c>
-      <c r="G122" s="61">
+      <c r="G122" s="3">
         <v>0.31903636455500001</v>
       </c>
-      <c r="H122" s="61">
+      <c r="H122" s="3">
         <v>3.0990045517700002E-2</v>
       </c>
-      <c r="I122" s="61">
+      <c r="I122" s="3">
         <v>-0.41003209352499997</v>
       </c>
-      <c r="J122" s="61">
+      <c r="J122" s="3">
         <v>0.15444207191500001</v>
       </c>
-      <c r="K122" s="61">
+      <c r="K122" s="3">
         <v>0.184084400535</v>
       </c>
-      <c r="L122" s="61">
+      <c r="L122" s="3">
         <v>0.100005038083</v>
       </c>
-      <c r="M122" s="61">
+      <c r="M122" s="3">
         <v>-0.55887258052800004</v>
       </c>
-      <c r="N122" s="61">
+      <c r="N122" s="3">
         <v>8.6099490523300001E-2</v>
       </c>
-      <c r="O122" s="61">
+      <c r="O122" s="3">
         <v>-2.5714814662900001E-2</v>
       </c>
-      <c r="P122" s="61">
+      <c r="P122" s="3">
         <v>-0.39875939488399997</v>
       </c>
-      <c r="Q122" s="61">
+      <c r="Q122" s="3">
         <v>0.11734274029699999</v>
       </c>
       <c r="U122" s="3">
@@ -6638,58 +6709,58 @@
       <c r="AA122" s="3">
         <v>-0.91840815544099996</v>
       </c>
-      <c r="AB122" s="50">
+      <c r="AB122" s="49">
         <v>0.108948364854</v>
       </c>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A123" s="60"/>
-      <c r="B123" s="61">
+      <c r="A123" s="55"/>
+      <c r="B123" s="3">
         <v>-1.0215300135299999E-3</v>
       </c>
-      <c r="C123" s="61">
+      <c r="C123" s="3">
         <v>-0.57288050651599998</v>
       </c>
-      <c r="D123" s="61">
+      <c r="D123" s="3">
         <v>-0.19400258362299999</v>
       </c>
-      <c r="E123" s="61">
+      <c r="E123" s="3">
         <v>-0.44583189487500002</v>
       </c>
-      <c r="F123" s="61">
+      <c r="F123" s="3">
         <v>0.78264307975799996</v>
       </c>
-      <c r="G123" s="61">
+      <c r="G123" s="3">
         <v>-0.24963971972499999</v>
       </c>
-      <c r="H123" s="61">
+      <c r="H123" s="3">
         <v>-7.3840908706199998E-2</v>
       </c>
-      <c r="I123" s="61">
+      <c r="I123" s="3">
         <v>0.95773655176200001</v>
       </c>
-      <c r="J123" s="61">
+      <c r="J123" s="3">
         <v>0.19428023695900001</v>
       </c>
-      <c r="K123" s="61">
+      <c r="K123" s="3">
         <v>-0.39871388673800001</v>
       </c>
-      <c r="L123" s="61">
+      <c r="L123" s="3">
         <v>-0.166650667787</v>
       </c>
-      <c r="M123" s="61">
+      <c r="M123" s="3">
         <v>0.22771453857400001</v>
       </c>
-      <c r="N123" s="61">
+      <c r="N123" s="3">
         <v>-0.16871072351899999</v>
       </c>
-      <c r="O123" s="61">
+      <c r="O123" s="3">
         <v>4.8592686653099997E-3</v>
       </c>
-      <c r="P123" s="61">
+      <c r="P123" s="3">
         <v>0.92990368604700002</v>
       </c>
-      <c r="Q123" s="61">
+      <c r="Q123" s="3">
         <v>-0.53339624404899999</v>
       </c>
       <c r="U123" s="3">
@@ -6713,12 +6784,12 @@
       <c r="AA123" s="3">
         <v>-0.22353570163200001</v>
       </c>
-      <c r="AB123" s="50">
+      <c r="AB123" s="49">
         <v>0.35477641224899997</v>
       </c>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A124" s="60"/>
+      <c r="A124" s="55"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
@@ -6742,87 +6813,87 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
       <c r="AA124" s="3"/>
-      <c r="AB124" s="50"/>
+      <c r="AB124" s="49"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A125" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B125" s="52">
+      <c r="A125" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="B125" s="51">
         <v>8.0120123922800005E-2</v>
       </c>
-      <c r="C125" s="52">
+      <c r="C125" s="51">
         <v>-0.32195743918399999</v>
       </c>
-      <c r="D125" s="52">
+      <c r="D125" s="51">
         <v>-0.264730751514</v>
       </c>
-      <c r="E125" s="52">
+      <c r="E125" s="51">
         <v>-1.8011648207900001E-2</v>
       </c>
-      <c r="F125" s="52">
+      <c r="F125" s="51">
         <v>0.41245678067199998</v>
       </c>
-      <c r="G125" s="52">
+      <c r="G125" s="51">
         <v>-0.26637837290799998</v>
       </c>
-      <c r="H125" s="52">
+      <c r="H125" s="51">
         <v>0.16497224569300001</v>
       </c>
-      <c r="I125" s="52">
+      <c r="I125" s="51">
         <v>-9.1823756694800002E-2</v>
       </c>
-      <c r="J125" s="52">
+      <c r="J125" s="51">
         <v>-0.21360945701600001</v>
       </c>
-      <c r="K125" s="52">
+      <c r="K125" s="51">
         <v>0.21213024854699999</v>
       </c>
-      <c r="L125" s="52">
+      <c r="L125" s="51">
         <v>0.30172690749199998</v>
       </c>
-      <c r="M125" s="52">
+      <c r="M125" s="51">
         <v>0.228981569409</v>
       </c>
-      <c r="N125" s="52">
+      <c r="N125" s="51">
         <v>0.29625037312500002</v>
       </c>
-      <c r="O125" s="52">
+      <c r="O125" s="51">
         <v>-0.30695861578</v>
       </c>
-      <c r="P125" s="52">
+      <c r="P125" s="51">
         <v>0.168809562922</v>
       </c>
-      <c r="Q125" s="52">
+      <c r="Q125" s="51">
         <v>6.7095644772100005E-2</v>
       </c>
-      <c r="R125" s="55"/>
-      <c r="S125" s="55"/>
-      <c r="T125" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="U125" s="52">
+      <c r="R125" s="53"/>
+      <c r="S125" s="53"/>
+      <c r="T125" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="U125" s="51">
         <v>5.7242356240700003E-2</v>
       </c>
-      <c r="V125" s="52">
+      <c r="V125" s="51">
         <v>-0.16314640641200001</v>
       </c>
-      <c r="W125" s="52">
+      <c r="W125" s="51">
         <v>-0.26818734407400002</v>
       </c>
-      <c r="X125" s="52">
+      <c r="X125" s="51">
         <v>0.186604768038</v>
       </c>
-      <c r="Y125" s="52">
+      <c r="Y125" s="51">
         <v>0.24573500454399999</v>
       </c>
-      <c r="Z125" s="52">
+      <c r="Z125" s="51">
         <v>-0.204172313213</v>
       </c>
-      <c r="AA125" s="52">
+      <c r="AA125" s="51">
         <v>-0.25449725985499999</v>
       </c>
-      <c r="AB125" s="53">
+      <c r="AB125" s="52">
         <v>0.224094897509</v>
       </c>
     </row>
@@ -6846,613 +6917,535 @@
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>53</v>
-      </c>
-      <c r="B127" s="3">
-        <f>B111*B116+C111*B117+D111*B118+E111*B119+F111*B120+G111*B121+H111*B122+I111*B123+B$125</f>
+        <v>52</v>
+      </c>
+      <c r="B127" s="3" cm="1">
+        <f t="array" ref="B127:Q130">MMULT(B111:I114,B116:Q123)+B125:Q125</f>
         <v>2.8129597728333504</v>
       </c>
       <c r="C127" s="3">
-        <f>B111*C116+C111*C117+D111*C118+E111*C119+F111*C120+G111*C121+H111*C122+I111*C123+C$125</f>
         <v>1.0063028649573851</v>
       </c>
       <c r="D127" s="3">
-        <f>B111*D116+C111*D117+D111*D118+E111*D119+F111*D120+G111*D121+H111*D122+I111*D123+D$125</f>
         <v>-1.318127045077623</v>
       </c>
       <c r="E127" s="3">
-        <f>B111*E116+C111*E117+D111*E118+E111*E119+F111*E120+G111*E121+H111*E122+I111*E123+E$125</f>
         <v>0.58187793432641077</v>
       </c>
       <c r="F127" s="3">
-        <f>B111*F116+C111*F117+D111*F118+E111*F119+F111*F120+G111*F121+H111*F122+I111*F123+F$125</f>
         <v>-0.43267182220125333</v>
       </c>
       <c r="G127" s="3">
-        <f>B111*G116+C111*G117+D111*G118+E111*G119+F111*G120+G111*G121+H111*G122+I111*G123+G$125</f>
         <v>2.8009080538375115</v>
       </c>
       <c r="H127" s="3">
-        <f>B111*H116+C111*H117+D111*H118+E111*H119+F111*H120+G111*H121+H111*H122+I111*H123+H$125</f>
         <v>0.50095971727817434</v>
       </c>
       <c r="I127" s="3">
-        <f>B111*I116+C111*I117+D111*I118+E111*I119+F111*I120+G111*I121+H111*I122+I111*I123+I$125</f>
         <v>-1.6342099846426947</v>
       </c>
       <c r="J127" s="3">
-        <f>B111*J116+C111*J117+D111*J118+E111*J119+F111*J120+G111*J121+H111*J122+I111*J123+J$125</f>
         <v>0.34873707032801271</v>
       </c>
       <c r="K127" s="3">
-        <f>B111*K116+C111*K117+D111*K118+E111*K119+F111*K120+G111*K121+H111*K122+I111*K123+K$125</f>
         <v>0.90081905485482849</v>
       </c>
       <c r="L127" s="3">
-        <f>B111*L116+C111*L117+D111*L118+E111*L119+F111*L120+G111*L121+H111*L122+I111*L123+L$125</f>
         <v>1.1485237394984997</v>
       </c>
       <c r="M127" s="3">
-        <f>B111*M116+C111*M117+D111*M118+E111*M119+F111*M120+G111*M121+H111*M122+I111*M123+M$125</f>
         <v>2.17080990558786</v>
       </c>
       <c r="N127" s="3">
-        <f>B111*N116+C111*N117+D111*N118+E111*N119+F111*N120+G111*N121+H111*N122+I111*N123+N$125</f>
         <v>2.2363586161416849</v>
       </c>
       <c r="O127" s="3">
-        <f>B111*O116+C111*O117+D111*O118+E111*O119+F111*O120+G111*O121+H111*O122+I111*O123+O$125</f>
         <v>0.18964266199821739</v>
       </c>
       <c r="P127" s="3">
-        <f>B111*P116+C111*P117+D111*P118+E111*P119+F111*P120+G111*P121+H111*P122+I111*P123+P$125</f>
         <v>-0.67996284789377537</v>
       </c>
       <c r="Q127" s="3">
-        <f>B111*Q116+C111*Q117+D111*Q118+E111*Q119+F111*Q120+G111*Q121+H111*Q122+I111*Q123+Q$125</f>
         <v>2.3302882047160489</v>
       </c>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B128" s="3">
-        <f>B112*B116+C112*B117+D112*B118+E112*B119+F112*B120+G112*B121+H112*B122+I112*B123+B$125</f>
         <v>1.314399858706828</v>
       </c>
       <c r="C128" s="3">
-        <f>B112*C116+C112*C117+D112*C118+E112*C119+F112*C120+G112*C121+H112*C122+I112*C123+C$125</f>
         <v>1.0504603000949309</v>
       </c>
       <c r="D128" s="3">
-        <f>B112*D116+C112*D117+D112*D118+E112*D119+F112*D120+G112*D121+H112*D122+I112*D123+D$125</f>
         <v>-1.3226128672096762</v>
       </c>
       <c r="E128" s="3">
-        <f>B112*E116+C112*E117+D112*E118+E112*E119+F112*E120+G112*E121+H112*E122+I112*E123+E$125</f>
         <v>0.5261281914580811</v>
       </c>
       <c r="F128" s="3">
-        <f>B112*F116+C112*F117+D112*F118+E112*F119+F112*F120+G112*F121+H112*F122+I112*F123+F$125</f>
         <v>-0.66529742825480487</v>
       </c>
       <c r="G128" s="3">
-        <f>B112*G116+C112*G117+D112*G118+E112*G119+F112*G120+G112*G121+H112*G122+I112*G123+G$125</f>
         <v>1.5099076687057376</v>
       </c>
       <c r="H128" s="3">
-        <f>B112*H116+C112*H117+D112*H118+E112*H119+F112*H120+G112*H121+H112*H122+I112*H123+H$125</f>
         <v>1.1574079334603993</v>
       </c>
       <c r="I128" s="3">
-        <f>B112*I116+C112*I117+D112*I118+E112*I119+F112*I120+G112*I121+H112*I122+I112*I123+I$125</f>
         <v>-1.9781283175141244</v>
       </c>
       <c r="J128" s="3">
-        <f>B112*J116+C112*J117+D112*J118+E112*J119+F112*J120+G112*J121+H112*J122+I112*J123+J$125</f>
         <v>-9.7291992324095466E-2</v>
       </c>
       <c r="K128" s="3">
-        <f>B112*K116+C112*K117+D112*K118+E112*K119+F112*K120+G112*K121+H112*K122+I112*K123+K$125</f>
         <v>0.98190849233017163</v>
       </c>
       <c r="L128" s="3">
-        <f>B112*L116+C112*L117+D112*L118+E112*L119+F112*L120+G112*L121+H112*L122+I112*L123+L$125</f>
         <v>1.1581538936008651</v>
       </c>
       <c r="M128" s="3">
-        <f>B112*M116+C112*M117+D112*M118+E112*M119+F112*M120+G112*M121+H112*M122+I112*M123+M$125</f>
         <v>0.86061125374755609</v>
       </c>
       <c r="N128" s="3">
-        <f>B112*N116+C112*N117+D112*N118+E112*N119+F112*N120+G112*N121+H112*N122+I112*N123+N$125</f>
         <v>1.2044384166856799</v>
       </c>
       <c r="O128" s="3">
-        <f>B112*O116+C112*O117+D112*O118+E112*O119+F112*O120+G112*O121+H112*O122+I112*O123+O$125</f>
         <v>-0.24680514017998395</v>
       </c>
       <c r="P128" s="3">
-        <f>B112*P116+C112*P117+D112*P118+E112*P119+F112*P120+G112*P121+H112*P122+I112*P123+P$125</f>
         <v>-0.59705659055894522</v>
       </c>
       <c r="Q128" s="3">
-        <f>B112*Q116+C112*Q117+D112*Q118+E112*Q119+F112*Q120+G112*Q121+H112*Q122+I112*Q123+Q$125</f>
         <v>1.924390389014522</v>
       </c>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B129" s="3">
-        <f>B113*B116+C113*B117+D113*B118+E113*B119+F113*B120+G113*B121+H113*B122+I113*B123+B$125</f>
         <v>1.0322494614206421</v>
       </c>
       <c r="C129" s="3">
-        <f>B113*C116+C113*C117+D113*C118+E113*C119+F113*C120+G113*C121+H113*C122+I113*C123+C$125</f>
         <v>1.3395932594899134</v>
       </c>
       <c r="D129" s="3">
-        <f>B113*D116+C113*D117+D113*D118+E113*D119+F113*D120+G113*D121+H113*D122+I113*D123+D$125</f>
         <v>-0.1337861875900872</v>
       </c>
       <c r="E129" s="3">
-        <f>B113*E116+C113*E117+D113*E118+E113*E119+F113*E120+G113*E121+H113*E122+I113*E123+E$125</f>
         <v>-0.82660369291647373</v>
       </c>
       <c r="F129" s="3">
-        <f>B113*F116+C113*F117+D113*F118+E113*F119+F113*F120+G113*F121+H113*F122+I113*F123+F$125</f>
         <v>0.37093415419802633</v>
       </c>
       <c r="G129" s="3">
-        <f>B113*G116+C113*G117+D113*G118+E113*G119+F113*G120+G113*G121+H113*G122+I113*G123+G$125</f>
         <v>1.4539288450708072</v>
       </c>
       <c r="H129" s="3">
-        <f>B113*H116+C113*H117+D113*H118+E113*H119+F113*H120+G113*H121+H113*H122+I113*H123+H$125</f>
         <v>0.97656597115271104</v>
       </c>
       <c r="I129" s="3">
-        <f>B113*I116+C113*I117+D113*I118+E113*I119+F113*I120+G113*I121+H113*I122+I113*I123+I$125</f>
         <v>-0.70652681367869918</v>
       </c>
       <c r="J129" s="3">
-        <f>B113*J116+C113*J117+D113*J118+E113*J119+F113*J120+G113*J121+H113*J122+I113*J123+J$125</f>
         <v>0.50746472707297186</v>
       </c>
       <c r="K129" s="3">
-        <f>B113*K116+C113*K117+D113*K118+E113*K119+F113*K120+G113*K121+H113*K122+I113*K123+K$125</f>
         <v>0.99824643762807763</v>
       </c>
       <c r="L129" s="3">
-        <f>B113*L116+C113*L117+D113*L118+E113*L119+F113*L120+G113*L121+H113*L122+I113*L123+L$125</f>
         <v>-0.74539991624414359</v>
       </c>
       <c r="M129" s="3">
-        <f>B113*M116+C113*M117+D113*M118+E113*M119+F113*M120+G113*M121+H113*M122+I113*M123+M$125</f>
         <v>0.18614467486934153</v>
       </c>
       <c r="N129" s="3">
-        <f>B113*N116+C113*N117+D113*N118+E113*N119+F113*N120+G113*N121+H113*N122+I113*N123+N$125</f>
         <v>0.46522142506454967</v>
       </c>
       <c r="O129" s="3">
-        <f>B113*O116+C113*O117+D113*O118+E113*O119+F113*O120+G113*O121+H113*O122+I113*O123+O$125</f>
         <v>0.14176188923230731</v>
       </c>
       <c r="P129" s="3">
-        <f>B113*P116+C113*P117+D113*P118+E113*P119+F113*P120+G113*P121+H113*P122+I113*P123+P$125</f>
         <v>0.23074493224092896</v>
       </c>
       <c r="Q129" s="3">
-        <f>B113*Q116+C113*Q117+D113*Q118+E113*Q119+F113*Q120+G113*Q121+H113*Q122+I113*Q123+Q$125</f>
         <v>2.0967550181992478</v>
       </c>
     </row>
     <row r="130" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B130" s="3">
-        <f>B114*B116+C114*B117+D114*B118+E114*B119+F114*B120+G114*B121+H114*B122+I114*B123+B$125</f>
         <v>0.62258485326645407</v>
       </c>
       <c r="C130" s="3">
-        <f>B114*C116+C114*C117+D114*C118+E114*C119+F114*C120+G114*C121+H114*C122+I114*C123+C$125</f>
         <v>1.539131604459131</v>
       </c>
       <c r="D130" s="3">
-        <f>B114*D116+C114*D117+D114*D118+E114*D119+F114*D120+G114*D121+H114*D122+I114*D123+D$125</f>
         <v>-1.3278343758046702</v>
       </c>
       <c r="E130" s="3">
-        <f>B114*E116+C114*E117+D114*E118+E114*E119+F114*E120+G114*E121+H114*E122+I114*E123+E$125</f>
         <v>1.1630162403293904</v>
       </c>
       <c r="F130" s="3">
-        <f>B114*F116+C114*F117+D114*F118+E114*F119+F114*F120+G114*F121+H114*F122+I114*F123+F$125</f>
         <v>-2.2028471755134698</v>
       </c>
       <c r="G130" s="3">
-        <f>B114*G116+C114*G117+D114*G118+E114*G119+F114*G120+G114*G121+H114*G122+I114*G123+G$125</f>
         <v>1.5911118524239729</v>
       </c>
       <c r="H130" s="3">
-        <f>B114*H116+C114*H117+D114*H118+E114*H119+F114*H120+G114*H121+H114*H122+I114*H123+H$125</f>
         <v>0.6991800688192078</v>
       </c>
       <c r="I130" s="3">
-        <f>B114*I116+C114*I117+D114*I118+E114*I119+F114*I120+G114*I121+H114*I122+I114*I123+I$125</f>
         <v>-3.3688506609809536</v>
       </c>
       <c r="J130" s="3">
-        <f>B114*J116+C114*J117+D114*J118+E114*J119+F114*J120+G114*J121+H114*J122+I114*J123+J$125</f>
         <v>-0.30985417230161283</v>
       </c>
       <c r="K130" s="3">
-        <f>B114*K116+C114*K117+D114*K118+E114*K119+F114*K120+G114*K121+H114*K122+I114*K123+K$125</f>
         <v>1.2621957281963272</v>
       </c>
       <c r="L130" s="3">
-        <f>B114*L116+C114*L117+D114*L118+E114*L119+F114*L120+G114*L121+H114*L122+I114*L123+L$125</f>
         <v>1.8514874474812155</v>
       </c>
       <c r="M130" s="3">
-        <f>B114*M116+C114*M117+D114*M118+E114*M119+F114*M120+G114*M121+H114*M122+I114*M123+M$125</f>
         <v>0.48820499455007443</v>
       </c>
       <c r="N130" s="3">
-        <f>B114*N116+C114*N117+D114*N118+E114*N119+F114*N120+G114*N121+H114*N122+I114*N123+N$125</f>
         <v>1.5703115591718522</v>
       </c>
       <c r="O130" s="3">
-        <f>B114*O116+C114*O117+D114*O118+E114*O119+F114*O120+G114*O121+H114*O122+I114*O123+O$125</f>
         <v>-0.36409598821562011</v>
       </c>
       <c r="P130" s="3">
-        <f>B114*P116+C114*P117+D114*P118+E114*P119+F114*P120+G114*P121+H114*P122+I114*P123+P$125</f>
         <v>-2.1492201880877762</v>
       </c>
       <c r="Q130" s="3">
-        <f>B114*Q116+C114*Q117+D114*Q118+E114*Q119+F114*Q120+G114*Q121+H114*Q122+I114*Q123+Q$125</f>
         <v>1.718606789089304</v>
       </c>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B132" s="3">
-        <f t="shared" ref="B132:Q132" si="19">MAX(0,B127)</f>
+        <f t="shared" ref="B132:Q132" si="18">MAX(0,B127)</f>
         <v>2.8129597728333504</v>
       </c>
       <c r="C132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1.0063028649573851</v>
       </c>
       <c r="D132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="E132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.58187793432641077</v>
       </c>
       <c r="F132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.8009080538375115</v>
       </c>
       <c r="H132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.50095971727817434</v>
       </c>
       <c r="I132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.34873707032801271</v>
       </c>
       <c r="K132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.90081905485482849</v>
       </c>
       <c r="L132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1.1485237394984997</v>
       </c>
       <c r="M132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.17080990558786</v>
       </c>
       <c r="N132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.2363586161416849</v>
       </c>
       <c r="O132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.18964266199821739</v>
       </c>
       <c r="P132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q132" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.3302882047160489</v>
       </c>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B133" s="3">
-        <f t="shared" ref="B133:Q133" si="20">MAX(0,B128)</f>
+        <f t="shared" ref="B133:Q133" si="19">MAX(0,B128)</f>
         <v>1.314399858706828</v>
       </c>
       <c r="C133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.0504603000949309</v>
       </c>
       <c r="D133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0.5261281914580811</v>
       </c>
       <c r="F133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.5099076687057376</v>
       </c>
       <c r="H133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.1574079334603993</v>
       </c>
       <c r="I133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0.98190849233017163</v>
       </c>
       <c r="L133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.1581538936008651</v>
       </c>
       <c r="M133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0.86061125374755609</v>
       </c>
       <c r="N133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.2044384166856799</v>
       </c>
       <c r="O133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q133" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.924390389014522</v>
       </c>
     </row>
     <row r="134" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B134" s="3">
-        <f t="shared" ref="B134:Q134" si="21">MAX(0,B129)</f>
+        <f t="shared" ref="B134:Q134" si="20">MAX(0,B129)</f>
         <v>1.0322494614206421</v>
       </c>
       <c r="C134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>1.3395932594899134</v>
       </c>
       <c r="D134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.37093415419802633</v>
       </c>
       <c r="G134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>1.4539288450708072</v>
       </c>
       <c r="H134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.97656597115271104</v>
       </c>
       <c r="I134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.50746472707297186</v>
       </c>
       <c r="K134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.99824643762807763</v>
       </c>
       <c r="L134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.18614467486934153</v>
       </c>
       <c r="N134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.46522142506454967</v>
       </c>
       <c r="O134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.14176188923230731</v>
       </c>
       <c r="P134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.23074493224092896</v>
       </c>
       <c r="Q134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>2.0967550181992478</v>
       </c>
     </row>
     <row r="135" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B135" s="3">
-        <f t="shared" ref="B135:Q135" si="22">MAX(0,B130)</f>
+        <f t="shared" ref="B135:Q135" si="21">MAX(0,B130)</f>
         <v>0.62258485326645407</v>
       </c>
       <c r="C135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.539131604459131</v>
       </c>
       <c r="D135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.1630162403293904</v>
       </c>
       <c r="F135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="G135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.5911118524239729</v>
       </c>
       <c r="H135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0.6991800688192078</v>
       </c>
       <c r="I135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.2621957281963272</v>
       </c>
       <c r="L135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.8514874474812155</v>
       </c>
       <c r="M135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0.48820499455007443</v>
       </c>
       <c r="N135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.5703115591718522</v>
       </c>
       <c r="O135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="P135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q135" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>1.718606789089304</v>
       </c>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>54</v>
-      </c>
-      <c r="B137" s="3">
-        <f>B132*U108+C132*U109+D132*U110+E132*U111+F132*U112+G132*U113+H132*U114+I132*U115+J132*U116+K132*U117+L132*U118+M132*U119+N132*U120+O132*U121+P132*U122+Q132*U123+U$125</f>
+        <v>53</v>
+      </c>
+      <c r="B137" s="3" cm="1">
+        <f t="array" ref="B137:I140">MMULT(B132:Q135,U108:AB123)+U125:AB125</f>
         <v>2.2604590627412096</v>
       </c>
       <c r="C137" s="3">
-        <f>B132*V108+C132*V109+D132*V110+E132*V111+F132*V112+G132*V113+H132*V114+I132*V115+J132*V116+K132*V117+L132*V118+M132*V119+N132*V120+O132*V121+P132*V122+Q132*V123+V$125</f>
         <v>1.3640309031205922</v>
       </c>
       <c r="D137" s="3">
-        <f>B132*W108+C132*W109+D132*W110+E132*W111+F132*W112+G132*W113+H132*W114+I132*W115+J132*W116+K132*W117+L132*W118+M132*W119+N132*W120+O132*W121+P132*W122+Q132*W123+W$125</f>
         <v>2.0163258276871483</v>
       </c>
       <c r="E137" s="3">
-        <f>B132*X108+C132*X109+D132*X110+E132*X111+F132*X112+G132*X113+H132*X114+I132*X115+J132*X116+K132*X117+L132*X118+M132*X119+N132*X120+O132*X121+P132*X122+Q132*X123+X$125</f>
         <v>1.5164876794571356</v>
       </c>
       <c r="F137" s="3">
-        <f>B132*Y108+C132*Y109+D132*Y110+E132*Y111+F132*Y112+G132*Y113+H132*Y114+I132*Y115+J132*Y116+K132*Y117+L132*Y118+M132*Y119+N132*Y120+O132*Y121+P132*Y122+Q132*Y123+Y$125</f>
         <v>-2.8700598827651311</v>
       </c>
       <c r="G137" s="3">
-        <f>B132*Z108+C132*Z109+D132*Z110+E132*Z111+F132*Z112+G132*Z113+H132*Z114+I132*Z115+J132*Z116+K132*Z117+L132*Z118+M132*Z119+N132*Z120+O132*Z121+P132*Z122+Q132*Z123+Z$125</f>
         <v>-3.4673781848931444</v>
       </c>
       <c r="H137" s="3">
-        <f>B132*AA108+C132*AA109+D132*AA110+E132*AA111+F132*AA112+G132*AA113+H132*AA114+I132*AA115+J132*AA116+K132*AA117+L132*AA118+M132*AA119+N132*AA120+O132*AA121+P132*AA122+Q132*AA123+AA$125</f>
         <v>-3.2701257718809917</v>
       </c>
       <c r="I137" s="3">
-        <f>B132*AB108+C132*AB109+D132*AB110+E132*AB111+F132*AB112+G132*AB113+H132*AB114+I132*AB115+J132*AB116+K132*AB117+L132*AB118+M132*AB119+N132*AB120+O132*AB121+P132*AB122+Q132*AB123+AB$125</f>
         <v>0.45961216461215226</v>
       </c>
     </row>
     <row r="138" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B138" s="3">
-        <f>B133*U108+C133*U109+D133*U110+E133*U111+F133*U112+G133*U113+H133*U114+I133*U115+J133*U116+K133*U117+L133*U118+M133*U119+N133*U120+O133*U121+P133*U122+Q133*U123+U$125</f>
         <v>0.79852444327632255</v>
       </c>
       <c r="C138" s="3">
-        <f>B133*V108+C133*V109+D133*V110+E133*V111+F133*V112+G133*V113+H133*V114+I133*V115+J133*V116+K133*V117+L133*V118+M133*V119+N133*V120+O133*V121+P133*V122+Q133*V123+V$125</f>
         <v>0.31271774621321063</v>
       </c>
       <c r="D138" s="3">
-        <f>B133*W108+C133*W109+D133*W110+E133*W111+F133*W112+G133*W113+H133*W114+I133*W115+J133*W116+K133*W117+L133*W118+M133*W119+N133*W120+O133*W121+P133*W122+Q133*W123+W$125</f>
         <v>0.57202494481148747</v>
       </c>
       <c r="E138" s="3">
-        <f>B133*X108+C133*X109+D133*X110+E133*X111+F133*X112+G133*X113+H133*X114+I133*X115+J133*X116+K133*X117+L133*X118+M133*X119+N133*X120+O133*X121+P133*X122+Q133*X123+X$125</f>
         <v>0.57404523649165207</v>
       </c>
       <c r="F138" s="3">
-        <f>B133*Y108+C133*Y109+D133*Y110+E133*Y111+F133*Y112+G133*Y113+H133*Y114+I133*Y115+J133*Y116+K133*Y117+L133*Y118+M133*Y119+N133*Y120+O133*Y121+P133*Y122+Q133*Y123+Y$125</f>
         <v>-0.20985083374616464</v>
       </c>
       <c r="G138" s="3">
-        <f>B133*Z108+C133*Z109+D133*Z110+E133*Z111+F133*Z112+G133*Z113+H133*Z114+I133*Z115+J133*Z116+K133*Z117+L133*Z118+M133*Z119+N133*Z120+O133*Z121+P133*Z122+Q133*Z123+Z$125</f>
         <v>-2.4356884255335833</v>
       </c>
       <c r="H138" s="3">
-        <f>B133*AA108+C133*AA109+D133*AA110+E133*AA111+F133*AA112+G133*AA113+H133*AA114+I133*AA115+J133*AA116+K133*AA117+L133*AA118+M133*AA119+N133*AA120+O133*AA121+P133*AA122+Q133*AA123+AA$125</f>
         <v>-1.7283766270658663</v>
       </c>
       <c r="I138" s="3">
-        <f>B133*AB108+C133*AB109+D133*AB110+E133*AB111+F133*AB112+G133*AB113+H133*AB114+I133*AB115+J133*AB116+K133*AB117+L133*AB118+M133*AB119+N133*AB120+O133*AB121+P133*AB122+Q133*AB123+AB$125</f>
         <v>1.3602731666889927</v>
       </c>
       <c r="K138" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L138" s="3">
         <v>1.8542363643599999</v>
@@ -7481,39 +7474,31 @@
     </row>
     <row r="139" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B139" s="3">
-        <f>B134*U108+C134*U109+D134*U110+E134*U111+F134*U112+G134*U113+H134*U114+I134*U115+J134*U116+K134*U117+L134*U118+M134*U119+N134*U120+O134*U121+P134*U122+Q134*U123+U$125</f>
         <v>1.2305904990818428</v>
       </c>
       <c r="C139" s="3">
-        <f>B134*V108+C134*V109+D134*V110+E134*V111+F134*V112+G134*V113+H134*V114+I134*V115+J134*V116+K134*V117+L134*V118+M134*V119+N134*V120+O134*V121+P134*V122+Q134*V123+V$125</f>
         <v>1.2377136699657705</v>
       </c>
       <c r="D139" s="3">
-        <f>B134*W108+C134*W109+D134*W110+E134*W111+F134*W112+G134*W113+H134*W114+I134*W115+J134*W116+K134*W117+L134*W118+M134*W119+N134*W120+O134*W121+P134*W122+Q134*W123+W$125</f>
         <v>0.31528475956680768</v>
       </c>
       <c r="E139" s="3">
-        <f>B134*X108+C134*X109+D134*X110+E134*X111+F134*X112+G134*X113+H134*X114+I134*X115+J134*X116+K134*X117+L134*X118+M134*X119+N134*X120+O134*X121+P134*X122+Q134*X123+X$125</f>
         <v>0.18320122851522838</v>
       </c>
       <c r="F139" s="3">
-        <f>B134*Y108+C134*Y109+D134*Y110+E134*Y111+F134*Y112+G134*Y113+H134*Y114+I134*Y115+J134*Y116+K134*Y117+L134*Y118+M134*Y119+N134*Y120+O134*Y121+P134*Y122+Q134*Y123+Y$125</f>
         <v>-6.1371827288265846E-2</v>
       </c>
       <c r="G139" s="3">
-        <f>B134*Z108+C134*Z109+D134*Z110+E134*Z111+F134*Z112+G134*Z113+H134*Z114+I134*Z115+J134*Z116+K134*Z117+L134*Z118+M134*Z119+N134*Z120+O134*Z121+P134*Z122+Q134*Z123+Z$125</f>
         <v>-0.72727828747696166</v>
       </c>
       <c r="H139" s="3">
-        <f>B134*AA108+C134*AA109+D134*AA110+E134*AA111+F134*AA112+G134*AA113+H134*AA114+I134*AA115+J134*AA116+K134*AA117+L134*AA118+M134*AA119+N134*AA120+O134*AA121+P134*AA122+Q134*AA123+AA$125</f>
         <v>-1.9821452753297168</v>
       </c>
       <c r="I139" s="3">
-        <f>B134*AB108+C134*AB109+D134*AB110+E134*AB111+F134*AB112+G134*AB113+H134*AB114+I134*AB115+J134*AB116+K134*AB117+L134*AB118+M134*AB119+N134*AB120+O134*AB121+P134*AB122+Q134*AB123+AB$125</f>
         <v>9.3733805234917117E-2</v>
       </c>
       <c r="K139" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L139" s="3">
         <v>-0.52721828222300005</v>
@@ -7542,35 +7527,27 @@
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B140" s="3">
-        <f>B135*U108+C135*U109+D135*U110+E135*U111+F135*U112+G135*U113+H135*U114+I135*U115+J135*U116+K135*U117+L135*U118+M135*U119+N135*U120+O135*U121+P135*U122+Q135*U123+U$125</f>
         <v>-0.33023270476064404</v>
       </c>
       <c r="C140" s="3">
-        <f>B135*V108+C135*V109+D135*V110+E135*V111+F135*V112+G135*V113+H135*V114+I135*V115+J135*V116+K135*V117+L135*V118+M135*V119+N135*V120+O135*V121+P135*V122+Q135*V123+V$125</f>
         <v>-0.19530243346307063</v>
       </c>
       <c r="D140" s="3">
-        <f>B135*W108+C135*W109+D135*W110+E135*W111+F135*W112+G135*W113+H135*W114+I135*W115+J135*W116+K135*W117+L135*W118+M135*W119+N135*W120+O135*W121+P135*W122+Q135*W123+W$125</f>
         <v>9.2423460823575998E-2</v>
       </c>
       <c r="E140" s="3">
-        <f>B135*X108+C135*X109+D135*X110+E135*X111+F135*X112+G135*X113+H135*X114+I135*X115+J135*X116+K135*X117+L135*X118+M135*X119+N135*X120+O135*X121+P135*X122+Q135*X123+X$125</f>
         <v>-0.56447047557189145</v>
       </c>
       <c r="F140" s="3">
-        <f>B135*Y108+C135*Y109+D135*Y110+E135*Y111+F135*Y112+G135*Y113+H135*Y114+I135*Y115+J135*Y116+K135*Y117+L135*Y118+M135*Y119+N135*Y120+O135*Y121+P135*Y122+Q135*Y123+Y$125</f>
         <v>-0.36243080407132044</v>
       </c>
       <c r="G140" s="3">
-        <f>B135*Z108+C135*Z109+D135*Z110+E135*Z111+F135*Z112+G135*Z113+H135*Z114+I135*Z115+J135*Z116+K135*Z117+L135*Z118+M135*Z119+N135*Z120+O135*Z121+P135*Z122+Q135*Z123+Z$125</f>
         <v>-1.7833527553311899</v>
       </c>
       <c r="H140" s="3">
-        <f>B135*AA108+C135*AA109+D135*AA110+E135*AA111+F135*AA112+G135*AA113+H135*AA114+I135*AA115+J135*AA116+K135*AA117+L135*AA118+M135*AA119+N135*AA120+O135*AA121+P135*AA122+Q135*AA123+AA$125</f>
         <v>-0.67413444116624555</v>
       </c>
       <c r="I140" s="3">
-        <f>B135*AB108+C135*AB109+D135*AB110+E135*AB111+F135*AB112+G135*AB113+H135*AB114+I135*AB115+J135*AB116+K135*AB117+L135*AB118+M135*AB119+N135*AB120+O135*AB121+P135*AB122+Q135*AB123+AB$125</f>
         <v>1.9497165102585727</v>
       </c>
     </row>
@@ -7584,43 +7561,43 @@
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
       <c r="Q141" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="142" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B142" s="3">
-        <f t="shared" ref="B142:I145" si="23">B137+B111</f>
+        <f t="shared" ref="B142:I145" si="22">B137+B111</f>
         <v>3.7353460783986856</v>
       </c>
       <c r="C142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2.0621121416860344</v>
       </c>
       <c r="D142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1.036588420520705</v>
       </c>
       <c r="E142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0.43446366880565068</v>
       </c>
       <c r="F142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-2.5308332659896982</v>
       </c>
       <c r="G142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-2.8476114035900046</v>
       </c>
       <c r="H142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-3.0266992101984713</v>
       </c>
       <c r="I142" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-1.4974424662739365</v>
       </c>
       <c r="Q142" s="3">
@@ -7662,38 +7639,38 @@
     </row>
     <row r="143" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0.79881532184492321</v>
       </c>
       <c r="C143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1.0892248506876179</v>
       </c>
       <c r="D143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.67585511131405684</v>
       </c>
       <c r="E143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0.15649957360538636</v>
       </c>
       <c r="F143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.54814094267516444</v>
       </c>
       <c r="G143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.63782314373781523</v>
       </c>
       <c r="H143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-1.6725376446728719</v>
       </c>
       <c r="I143" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0.28770935082122229</v>
       </c>
       <c r="Q143" s="3">
@@ -7735,35 +7712,35 @@
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1.7490364984695612</v>
       </c>
       <c r="C144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2.8957035918429685</v>
       </c>
       <c r="D144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.43306950128808563</v>
       </c>
       <c r="E144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.9288967425569451</v>
       </c>
       <c r="F144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.79033772959138893</v>
       </c>
       <c r="G144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.61983042190130277</v>
       </c>
       <c r="H144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-1.5044205767698489</v>
       </c>
       <c r="I144" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.62892477235893729</v>
       </c>
       <c r="Q144" s="3">
@@ -7805,35 +7782,35 @@
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-3.7126716771282819E-2</v>
       </c>
       <c r="C145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.37912180149758112</v>
       </c>
       <c r="D145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.60028844584534635</v>
       </c>
       <c r="E145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.46216087288284624</v>
       </c>
       <c r="F145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.51765137546180773</v>
       </c>
       <c r="G145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.111992367181178</v>
       </c>
       <c r="H145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-0.10250814119551188</v>
       </c>
       <c r="I145" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-5.1107058368329294E-2</v>
       </c>
       <c r="Q145" s="3">
@@ -7921,38 +7898,38 @@
     </row>
     <row r="147" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B147" s="3">
-        <f t="shared" ref="B147:I150" si="24">(B142-AVERAGE($B142:$I142))/SQRT(VARP($B142:$I142)+0.00001)*L$138+L$139</f>
+        <f t="shared" ref="B147:I150" si="23">(B142-AVERAGE($B142:$I142))/SQRT(VARP($B142:$I142)+0.00001)*L$138+L$139</f>
         <v>2.6676914711914494</v>
       </c>
       <c r="C147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2.1170409324408483</v>
       </c>
       <c r="D147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.3369880122196076</v>
       </c>
       <c r="E147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0.58305752342382311</v>
       </c>
       <c r="F147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.5187440999249369</v>
       </c>
       <c r="G147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.7088215195992964</v>
       </c>
       <c r="H147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-2.5820558936171634</v>
       </c>
       <c r="I147" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.1665220355136932</v>
       </c>
       <c r="Q147" s="3">
@@ -7994,35 +7971,35 @@
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.5553186873861384</v>
       </c>
       <c r="C148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2.9726080971937239</v>
       </c>
       <c r="D148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.1378136477855547</v>
       </c>
       <c r="E148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0.65593788622132121</v>
       </c>
       <c r="F148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.52601498348268971</v>
       </c>
       <c r="G148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.59576401770684051</v>
       </c>
       <c r="H148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-4.0374492196108083</v>
       </c>
       <c r="I148" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0.89392219845390697</v>
       </c>
       <c r="Q148" s="3">
@@ -8064,35 +8041,35 @@
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.7976010157347071</v>
       </c>
       <c r="C149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>4.0942236861515902</v>
       </c>
       <c r="D149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.43688389377935805</v>
       </c>
       <c r="E149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.188518828600917</v>
       </c>
       <c r="F149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.6599892255109554</v>
       </c>
       <c r="G149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.22433020102983403</v>
       </c>
       <c r="H149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-2.343816347351841</v>
       </c>
       <c r="I149" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.0129316301884044</v>
       </c>
       <c r="Q149" s="3">
@@ -8134,41 +8111,41 @@
     </row>
     <row r="150" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.5814072059744508</v>
       </c>
       <c r="C150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-0.63995643051398698</v>
       </c>
       <c r="D150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-2.8857266946904128</v>
       </c>
       <c r="E150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.5595858781036815</v>
       </c>
       <c r="F150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1.8500531842555412</v>
       </c>
       <c r="G150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2.50694291210054</v>
       </c>
       <c r="H150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.7931562127949334</v>
       </c>
       <c r="I150" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>2.0205657912533721</v>
       </c>
     </row>
     <row r="151" spans="1:28" x14ac:dyDescent="0.25">
       <c r="P151" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q151" s="3">
         <v>-0.68481963872899998</v>
@@ -8247,7 +8224,7 @@
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B153" s="3">
         <f>B147*Q142+C147*Q143+D147*Q144+E147*Q145+F147*Q146+G147*Q147+H147*Q148+I147*Q149+Q$151</f>
@@ -8300,7 +8277,7 @@
     </row>
     <row r="154" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B154" s="3">
         <f>B148*Q142+C148*Q143+D148*Q144+E148*Q145+F148*Q146+G148*Q147+H148*Q148+I148*Q149+Q$151</f>
@@ -8494,7 +8471,7 @@
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A159" t="str" cm="1">
-        <f t="array" ref="A159:A162">A18:A21</f>
+        <f t="array" ref="A159:A162">C18:C21</f>
         <v>one</v>
       </c>
       <c r="B159" s="1">
@@ -8931,19 +8908,19 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="20"/>
-      <c r="L1" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="19"/>
+      <c r="L1" s="16"/>
       <c r="M1">
         <v>146</v>
       </c>
@@ -8955,7 +8932,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
+      <c r="A2" s="16"/>
       <c r="B2">
         <v>146</v>
       </c>
@@ -8965,12 +8942,12 @@
       <c r="D2">
         <v>80</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="L2" s="18"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="41"/>
+      <c r="L2" s="17"/>
       <c r="M2">
         <v>0</v>
       </c>
@@ -8980,22 +8957,22 @@
       <c r="O2">
         <v>240</v>
       </c>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="39">
+      <c r="Q2" s="39"/>
+      <c r="R2" s="38">
         <f>SQRT((M1^2+M2^2)/2)</f>
         <v>103.23759005323593</v>
       </c>
-      <c r="S2" s="39">
+      <c r="S2" s="38">
         <f>SQRT((N1^2+N2^2)/2)</f>
         <v>192.66551326067673</v>
       </c>
-      <c r="T2" s="39">
+      <c r="T2" s="38">
         <f>SQRT((O1^2+O2^2)/2)</f>
         <v>178.88543819998318</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+      <c r="A3" s="17"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -9005,17 +8982,17 @@
       <c r="D3">
         <v>240</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="43"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
+      <c r="A4" s="18"/>
       <c r="B4">
         <v>241</v>
       </c>
@@ -9025,12 +9002,12 @@
       <c r="D4">
         <v>131</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="45"/>
-      <c r="L4" s="17"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="44"/>
+      <c r="L4" s="16"/>
       <c r="M4">
         <v>146</v>
       </c>
@@ -9040,12 +9017,12 @@
       <c r="O4">
         <v>80</v>
       </c>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
+      <c r="A5" s="19"/>
       <c r="B5">
         <v>216</v>
       </c>
@@ -9055,12 +9032,12 @@
       <c r="D5">
         <v>205</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="20"/>
-      <c r="L5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="19"/>
+      <c r="L5" s="18"/>
       <c r="M5">
         <v>241</v>
       </c>
@@ -9070,27 +9047,27 @@
       <c r="O5">
         <v>131</v>
       </c>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="39">
+      <c r="Q5" s="40"/>
+      <c r="R5" s="38">
         <f>SQRT((M4^2+M5^2)/2)</f>
         <v>199.24482427405738</v>
       </c>
-      <c r="S5" s="39">
+      <c r="S5" s="38">
         <f>SQRT((N4^2+N5^2)/2)</f>
         <v>189.50593658247226</v>
       </c>
-      <c r="T5" s="39">
+      <c r="T5" s="38">
         <f>SQRT((O4^2+O5^2)/2)</f>
         <v>108.53801177467736</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L7" s="17"/>
+      <c r="L7" s="16"/>
       <c r="M7">
         <v>146</v>
       </c>
@@ -9100,12 +9077,12 @@
       <c r="O7">
         <v>80</v>
       </c>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L8" s="20"/>
+      <c r="L8" s="19"/>
       <c r="M8">
         <v>216</v>
       </c>
@@ -9115,27 +9092,27 @@
       <c r="O8">
         <v>205</v>
       </c>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="39">
+      <c r="Q8" s="41"/>
+      <c r="R8" s="38">
         <f>SQRT((M7^2+M8^2)/2)</f>
         <v>184.3529224069963</v>
       </c>
-      <c r="S8" s="39">
+      <c r="S8" s="38">
         <f>SQRT((N7^2+N8^2)/2)</f>
         <v>166.04969135773786</v>
       </c>
-      <c r="T8" s="39">
+      <c r="T8" s="38">
         <f>SQRT((O7^2+O8^2)/2)</f>
         <v>155.60366319595437</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R9" s="39"/>
-      <c r="S9" s="39"/>
-      <c r="T9" s="39"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L10" s="18"/>
+      <c r="L10" s="17"/>
       <c r="M10">
         <v>0</v>
       </c>
@@ -9145,12 +9122,12 @@
       <c r="O10">
         <v>240</v>
       </c>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="39"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L11" s="19"/>
+      <c r="L11" s="18"/>
       <c r="M11">
         <v>241</v>
       </c>
@@ -9160,27 +9137,27 @@
       <c r="O11">
         <v>131</v>
       </c>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="39">
+      <c r="Q11" s="42"/>
+      <c r="R11" s="38">
         <f>SQRT((M10^2+M11^2)/2)</f>
         <v>170.41273426595797</v>
       </c>
-      <c r="S11" s="39">
+      <c r="S11" s="38">
         <f>SQRT((N10^2+N11^2)/2)</f>
         <v>172.53550359273885</v>
       </c>
-      <c r="T11" s="39">
+      <c r="T11" s="38">
         <f>SQRT((O10^2+O11^2)/2)</f>
         <v>193.34037343503815</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L13" s="18"/>
+      <c r="L13" s="17"/>
       <c r="M13">
         <v>0</v>
       </c>
@@ -9190,12 +9167,12 @@
       <c r="O13">
         <v>240</v>
       </c>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L14" s="20"/>
+      <c r="L14" s="19"/>
       <c r="M14">
         <v>216</v>
       </c>
@@ -9205,27 +9182,27 @@
       <c r="O14">
         <v>205</v>
       </c>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="39">
+      <c r="Q14" s="43"/>
+      <c r="R14" s="38">
         <f>SQRT((M13^2+M14^2)/2)</f>
         <v>152.73506473629428</v>
       </c>
-      <c r="S14" s="39">
+      <c r="S14" s="38">
         <f>SQRT((N13^2+N14^2)/2)</f>
         <v>146.38476696705843</v>
       </c>
-      <c r="T14" s="39">
+      <c r="T14" s="38">
         <f>SQRT((O13^2+O14^2)/2)</f>
         <v>223.18714120665643</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L16" s="19"/>
+      <c r="L16" s="18"/>
       <c r="M16">
         <v>241</v>
       </c>
@@ -9235,12 +9212,12 @@
       <c r="O16">
         <v>131</v>
       </c>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="39"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
     </row>
     <row r="17" spans="12:20" x14ac:dyDescent="0.25">
-      <c r="L17" s="20"/>
+      <c r="L17" s="19"/>
       <c r="M17">
         <v>216</v>
       </c>
@@ -9250,16 +9227,16 @@
       <c r="O17">
         <v>205</v>
       </c>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="39">
+      <c r="Q17" s="44"/>
+      <c r="R17" s="38">
         <f>SQRT((M16^2+M17^2)/2)</f>
         <v>228.84164830729569</v>
       </c>
-      <c r="S17" s="39">
+      <c r="S17" s="38">
         <f>SQRT((N16^2+N17^2)/2)</f>
         <v>142.20056258679148</v>
       </c>
-      <c r="T17" s="39">
+      <c r="T17" s="38">
         <f>SQRT((O16^2+O17^2)/2)</f>
         <v>172.02616080119907</v>
       </c>
